--- a/BMRN.xlsx
+++ b/BMRN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93C997B3-3DCF-4CF1-B9B2-8227B8F649B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17ED6DA0-B3F8-4516-AACD-83FABC8EF62F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="2470" windowWidth="16760" windowHeight="11340" activeTab="1" xr2:uid="{1A28BDC2-CB33-447E-AED0-8D4C76155960}"/>
+    <workbookView xWindow="19020" yWindow="10770" windowWidth="19170" windowHeight="13220" activeTab="1" xr2:uid="{1A28BDC2-CB33-447E-AED0-8D4C76155960}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="187">
   <si>
     <t>Price</t>
   </si>
@@ -589,6 +589,18 @@
   </si>
   <si>
     <t>BMN370 - vWD discontinued</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
+  <si>
+    <t>Q126</t>
   </si>
 </sst>
 </file>
@@ -770,7 +782,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -850,11 +862,7 @@
     <xf numFmtId="4" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -929,13 +937,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>35</xdr:col>
+      <xdr:col>39</xdr:col>
       <xdr:colOff>65614</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>63500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>35</xdr:col>
+      <xdr:col>39</xdr:col>
       <xdr:colOff>65614</xdr:colOff>
       <xdr:row>46</xdr:row>
       <xdr:rowOff>134937</xdr:rowOff>
@@ -1600,7 +1608,7 @@
       <c r="H16" s="9"/>
     </row>
     <row r="17" spans="2:8" ht="13" x14ac:dyDescent="0.3">
-      <c r="B17" s="50" t="s">
+      <c r="B17" s="49" t="s">
         <v>45</v>
       </c>
       <c r="C17" s="23" t="s">
@@ -1631,7 +1639,7 @@
       <c r="H18" s="12"/>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="51" t="s">
+      <c r="B20" t="s">
         <v>182</v>
       </c>
     </row>
@@ -1656,7 +1664,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1997BFD-C986-43B5-AFE7-A2D1E0EBF425}">
-  <dimension ref="A1:DR75"/>
+  <dimension ref="A1:DV75"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -1664,15 +1672,16 @@
     <col min="3" max="22" width="9.1796875" style="3"/>
     <col min="23" max="25" width="8.7265625" style="3"/>
     <col min="26" max="26" width="9.1796875" style="3"/>
-    <col min="43" max="43" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="27" max="30" width="8.7265625" style="3"/>
+    <col min="47" max="47" width="11.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:45" x14ac:dyDescent="0.25">
       <c r="C2" s="3" t="s">
         <v>51</v>
       </c>
@@ -1745,59 +1754,71 @@
       <c r="Z2" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="AC2">
+      <c r="AA2" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="AC2" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="AD2" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="AG2">
         <v>2018</v>
       </c>
-      <c r="AD2">
-        <f>+AC2+1</f>
+      <c r="AH2">
+        <f>+AG2+1</f>
         <v>2019</v>
       </c>
-      <c r="AE2">
-        <f>+AD2+1</f>
+      <c r="AI2">
+        <f>+AH2+1</f>
         <v>2020</v>
       </c>
-      <c r="AF2">
-        <f>+AE2+1</f>
+      <c r="AJ2">
+        <f>+AI2+1</f>
         <v>2021</v>
       </c>
-      <c r="AG2">
-        <f t="shared" ref="AG2:AO2" si="0">+AF2+1</f>
+      <c r="AK2">
+        <f t="shared" ref="AK2:AS2" si="0">+AJ2+1</f>
         <v>2022</v>
       </c>
-      <c r="AH2">
+      <c r="AL2">
         <f t="shared" si="0"/>
         <v>2023</v>
       </c>
-      <c r="AI2">
+      <c r="AM2">
         <f t="shared" si="0"/>
         <v>2024</v>
       </c>
-      <c r="AJ2">
+      <c r="AN2">
         <f t="shared" si="0"/>
         <v>2025</v>
       </c>
-      <c r="AK2">
+      <c r="AO2">
         <f t="shared" si="0"/>
         <v>2026</v>
       </c>
-      <c r="AL2">
+      <c r="AP2">
         <f t="shared" si="0"/>
         <v>2027</v>
       </c>
-      <c r="AM2">
+      <c r="AQ2">
         <f t="shared" si="0"/>
         <v>2028</v>
       </c>
-      <c r="AN2">
+      <c r="AR2">
         <f t="shared" si="0"/>
         <v>2029</v>
       </c>
-      <c r="AO2">
+      <c r="AS2">
         <f t="shared" si="0"/>
         <v>2030</v>
       </c>
     </row>
-    <row r="3" spans="1:41" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:45" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
         <v>84</v>
       </c>
@@ -1833,8 +1854,12 @@
       <c r="X3" s="25"/>
       <c r="Y3" s="25"/>
       <c r="Z3" s="25"/>
-    </row>
-    <row r="4" spans="1:41" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA3" s="25"/>
+      <c r="AB3" s="25"/>
+      <c r="AC3" s="25"/>
+      <c r="AD3" s="25"/>
+    </row>
+    <row r="4" spans="1:45" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
         <v>85</v>
       </c>
@@ -1870,8 +1895,12 @@
       <c r="X4" s="25"/>
       <c r="Y4" s="25"/>
       <c r="Z4" s="25"/>
-    </row>
-    <row r="5" spans="1:41" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA4" s="25"/>
+      <c r="AB4" s="25"/>
+      <c r="AC4" s="25"/>
+      <c r="AD4" s="25"/>
+    </row>
+    <row r="5" spans="1:45" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>87</v>
       </c>
@@ -1907,8 +1936,12 @@
       <c r="X5" s="25"/>
       <c r="Y5" s="25"/>
       <c r="Z5" s="25"/>
-    </row>
-    <row r="6" spans="1:41" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA5" s="25"/>
+      <c r="AB5" s="25"/>
+      <c r="AC5" s="25"/>
+      <c r="AD5" s="25"/>
+    </row>
+    <row r="6" spans="1:45" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
         <v>86</v>
       </c>
@@ -1944,15 +1977,19 @@
       <c r="X6" s="25"/>
       <c r="Y6" s="25"/>
       <c r="Z6" s="25"/>
-    </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AA6" s="25"/>
+      <c r="AB6" s="25"/>
+      <c r="AC6" s="25"/>
+      <c r="AD6" s="25"/>
+    </row>
+    <row r="7" spans="1:45" x14ac:dyDescent="0.25">
       <c r="H7" s="25"/>
       <c r="I7" s="25"/>
       <c r="J7" s="25"/>
       <c r="K7" s="25"/>
       <c r="L7" s="25"/>
     </row>
-    <row r="8" spans="1:41" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:45" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>77</v>
       </c>
@@ -2027,54 +2064,60 @@
         <f>+V8*1.05</f>
         <v>200.55</v>
       </c>
-      <c r="AD8" s="2">
+      <c r="AA8" s="25">
+        <v>210</v>
+      </c>
+      <c r="AB8" s="25"/>
+      <c r="AC8" s="25"/>
+      <c r="AD8" s="25"/>
+      <c r="AH8" s="2">
         <v>544.29999999999995</v>
       </c>
-      <c r="AE8" s="2">
+      <c r="AI8" s="2">
         <v>544.4</v>
       </c>
-      <c r="AF8" s="2">
+      <c r="AJ8" s="2">
         <f>SUM(G8:J8)</f>
         <v>623.25500000000011</v>
       </c>
-      <c r="AG8" s="2">
+      <c r="AK8" s="2">
         <f>SUM(K8:N8)</f>
         <v>663.77600000000007</v>
       </c>
-      <c r="AH8" s="2">
-        <f>SUM(O8:R8)</f>
+      <c r="AL8" s="2">
+        <f t="shared" ref="AL8:AL15" si="1">SUM(O8:R8)</f>
         <v>701.08400000000006</v>
       </c>
-      <c r="AI8" s="2">
-        <f>SUM(S8:V8)</f>
+      <c r="AM8" s="2">
+        <f t="shared" ref="AM8:AM15" si="2">SUM(S8:V8)</f>
         <v>739.53600000000006</v>
       </c>
-      <c r="AJ8" s="2">
-        <f>SUM(W8:Z8)</f>
+      <c r="AN8" s="2">
+        <f t="shared" ref="AN8:AN15" si="3">SUM(W8:Z8)</f>
         <v>762.36680000000001</v>
       </c>
-      <c r="AK8" s="2">
-        <f t="shared" ref="AK8:AO8" si="1">+AJ8*1.04</f>
+      <c r="AO8" s="2">
+        <f t="shared" ref="AO8:AS8" si="4">+AN8*1.04</f>
         <v>792.86147200000005</v>
       </c>
-      <c r="AL8" s="2">
-        <f t="shared" si="1"/>
+      <c r="AP8" s="2">
+        <f t="shared" si="4"/>
         <v>824.5759308800001</v>
       </c>
-      <c r="AM8" s="2">
-        <f t="shared" si="1"/>
+      <c r="AQ8" s="2">
+        <f t="shared" si="4"/>
         <v>857.55896811520017</v>
       </c>
-      <c r="AN8" s="2">
-        <f t="shared" si="1"/>
+      <c r="AR8" s="2">
+        <f t="shared" si="4"/>
         <v>891.86132683980816</v>
       </c>
-      <c r="AO8" s="2">
-        <f t="shared" si="1"/>
+      <c r="AS8" s="2">
+        <f t="shared" si="4"/>
         <v>927.53577991340046</v>
       </c>
     </row>
-    <row r="9" spans="1:41" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:45" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>155</v>
       </c>
@@ -2133,46 +2176,52 @@
         <f>+Y9+1</f>
         <v>14</v>
       </c>
-      <c r="AF9" s="2">
+      <c r="AA9" s="25">
+        <v>3</v>
+      </c>
+      <c r="AB9" s="25"/>
+      <c r="AC9" s="25"/>
+      <c r="AD9" s="25"/>
+      <c r="AJ9" s="2">
         <v>0</v>
       </c>
-      <c r="AG9" s="2">
+      <c r="AK9" s="2">
         <v>0</v>
       </c>
-      <c r="AH9" s="2">
-        <f>SUM(O9:R9)</f>
+      <c r="AL9" s="2">
+        <f t="shared" si="1"/>
         <v>3.5</v>
       </c>
-      <c r="AI9" s="2">
-        <f>SUM(S9:V9)</f>
+      <c r="AM9" s="2">
+        <f t="shared" si="2"/>
         <v>26.280999999999999</v>
       </c>
-      <c r="AJ9" s="2">
-        <f>SUM(W9:Z9)</f>
+      <c r="AN9" s="2">
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
-      <c r="AK9" s="2">
-        <f>+AJ9*1.3</f>
+      <c r="AO9" s="2">
+        <f>+AN9*1.3</f>
         <v>65</v>
       </c>
-      <c r="AL9" s="2">
-        <f>+AK9*1.2</f>
+      <c r="AP9" s="2">
+        <f>+AO9*1.2</f>
         <v>78</v>
       </c>
-      <c r="AM9" s="2">
-        <f>+AL9*1.2</f>
+      <c r="AQ9" s="2">
+        <f>+AP9*1.2</f>
         <v>93.6</v>
       </c>
-      <c r="AN9" s="2">
-        <f>+AM9*1.2</f>
+      <c r="AR9" s="2">
+        <f>+AQ9*1.2</f>
         <v>112.32</v>
       </c>
-      <c r="AO9" s="2">
-        <f>+AN9*1.15</f>
+      <c r="AS9" s="2">
+        <f>+AR9*1.15</f>
         <v>129.16799999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:41" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:45" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>78</v>
       </c>
@@ -2247,54 +2296,60 @@
         <f>+V10</f>
         <v>110</v>
       </c>
-      <c r="AD10" s="2">
+      <c r="AA10" s="25">
+        <v>130</v>
+      </c>
+      <c r="AB10" s="25"/>
+      <c r="AC10" s="25"/>
+      <c r="AD10" s="25"/>
+      <c r="AH10" s="2">
         <v>374.3</v>
       </c>
-      <c r="AE10" s="2">
+      <c r="AI10" s="2">
         <v>391.3</v>
       </c>
-      <c r="AF10" s="2">
-        <f t="shared" ref="AF10:AF22" si="2">SUM(G10:J10)</f>
+      <c r="AJ10" s="2">
+        <f t="shared" ref="AJ10:AJ22" si="5">SUM(G10:J10)</f>
         <v>380.41300000000001</v>
       </c>
-      <c r="AG10" s="2">
-        <f t="shared" ref="AG10:AG22" si="3">SUM(K10:N10)</f>
+      <c r="AK10" s="2">
+        <f t="shared" ref="AK10:AK22" si="6">SUM(K10:N10)</f>
         <v>443.78899999999999</v>
       </c>
-      <c r="AH10" s="2">
-        <f>SUM(O10:R10)</f>
+      <c r="AL10" s="2">
+        <f t="shared" si="1"/>
         <v>420.32400000000001</v>
       </c>
-      <c r="AI10" s="2">
-        <f>SUM(S10:V10)</f>
+      <c r="AM10" s="2">
+        <f t="shared" si="2"/>
         <v>479.678</v>
       </c>
-      <c r="AJ10" s="2">
-        <f>SUM(W10:Z10)</f>
+      <c r="AN10" s="2">
+        <f t="shared" si="3"/>
         <v>488.04899999999998</v>
       </c>
-      <c r="AK10" s="2">
-        <f t="shared" ref="AI10:AO10" si="4">+AJ10*1.04</f>
+      <c r="AO10" s="2">
+        <f t="shared" ref="AO10:AS10" si="7">+AN10*1.04</f>
         <v>507.57096000000001</v>
       </c>
-      <c r="AL10" s="2">
-        <f t="shared" si="4"/>
+      <c r="AP10" s="2">
+        <f t="shared" si="7"/>
         <v>527.87379840000006</v>
       </c>
-      <c r="AM10" s="2">
-        <f t="shared" si="4"/>
+      <c r="AQ10" s="2">
+        <f t="shared" si="7"/>
         <v>548.98875033600007</v>
       </c>
-      <c r="AN10" s="2">
-        <f t="shared" si="4"/>
+      <c r="AR10" s="2">
+        <f t="shared" si="7"/>
         <v>570.94830034944005</v>
       </c>
-      <c r="AO10" s="2">
-        <f t="shared" si="4"/>
+      <c r="AS10" s="2">
+        <f t="shared" si="7"/>
         <v>593.78623236341764</v>
       </c>
     </row>
-    <row r="11" spans="1:41" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:45" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>79</v>
       </c>
@@ -2369,54 +2424,60 @@
         <f>+V11*1.1</f>
         <v>110.00000000000001</v>
       </c>
-      <c r="AD11" s="2">
+      <c r="AA11" s="25">
+        <v>90</v>
+      </c>
+      <c r="AB11" s="25"/>
+      <c r="AC11" s="25"/>
+      <c r="AD11" s="25"/>
+      <c r="AH11" s="2">
         <v>86.9</v>
       </c>
-      <c r="AE11" s="2">
+      <c r="AI11" s="2">
         <v>171</v>
       </c>
-      <c r="AF11" s="2">
+      <c r="AJ11" s="2">
+        <f t="shared" si="5"/>
+        <v>237.435</v>
+      </c>
+      <c r="AK11" s="2">
+        <f t="shared" si="6"/>
+        <v>255.04900000000004</v>
+      </c>
+      <c r="AL11" s="2">
+        <f t="shared" si="1"/>
+        <v>303.92</v>
+      </c>
+      <c r="AM11" s="2">
         <f t="shared" si="2"/>
-        <v>237.435</v>
-      </c>
-      <c r="AG11" s="2">
+        <v>355</v>
+      </c>
+      <c r="AN11" s="2">
         <f t="shared" si="3"/>
-        <v>255.04900000000004</v>
-      </c>
-      <c r="AH11" s="2">
-        <f>SUM(O11:R11)</f>
-        <v>303.92</v>
-      </c>
-      <c r="AI11" s="2">
-        <f>SUM(S11:V11)</f>
-        <v>355</v>
-      </c>
-      <c r="AJ11" s="2">
-        <f>SUM(W11:Z11)</f>
         <v>400.2201</v>
       </c>
-      <c r="AK11" s="2">
-        <f t="shared" ref="AI11:AO11" si="5">+AJ11*1.05</f>
+      <c r="AO11" s="2">
+        <f t="shared" ref="AO11:AS11" si="8">+AN11*1.05</f>
         <v>420.23110500000001</v>
       </c>
-      <c r="AL11" s="2">
-        <f t="shared" si="5"/>
+      <c r="AP11" s="2">
+        <f t="shared" si="8"/>
         <v>441.24266025000003</v>
       </c>
-      <c r="AM11" s="2">
-        <f t="shared" si="5"/>
+      <c r="AQ11" s="2">
+        <f t="shared" si="8"/>
         <v>463.30479326250003</v>
       </c>
-      <c r="AN11" s="2">
-        <f t="shared" si="5"/>
+      <c r="AR11" s="2">
+        <f t="shared" si="8"/>
         <v>486.47003292562505</v>
       </c>
-      <c r="AO11" s="2">
-        <f t="shared" si="5"/>
+      <c r="AS11" s="2">
+        <f t="shared" si="8"/>
         <v>510.79353457190632</v>
       </c>
     </row>
-    <row r="12" spans="1:41" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:45" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
         <v>80</v>
       </c>
@@ -2491,54 +2552,60 @@
         <f>+Y12-1</f>
         <v>22</v>
       </c>
-      <c r="AD12" s="2">
+      <c r="AA12" s="25">
+        <v>24</v>
+      </c>
+      <c r="AB12" s="25"/>
+      <c r="AC12" s="25"/>
+      <c r="AD12" s="25"/>
+      <c r="AH12" s="2">
         <v>463.4</v>
       </c>
-      <c r="AE12" s="2">
+      <c r="AI12" s="2">
         <v>457.7</v>
       </c>
-      <c r="AF12" s="2">
+      <c r="AJ12" s="2">
+        <f t="shared" si="5"/>
+        <v>285.80700000000002</v>
+      </c>
+      <c r="AK12" s="2">
+        <f t="shared" si="6"/>
+        <v>227.54</v>
+      </c>
+      <c r="AL12" s="2">
+        <f t="shared" si="1"/>
+        <v>180.7</v>
+      </c>
+      <c r="AM12" s="2">
         <f t="shared" si="2"/>
-        <v>285.80700000000002</v>
-      </c>
-      <c r="AG12" s="2">
+        <v>120.461</v>
+      </c>
+      <c r="AN12" s="2">
         <f t="shared" si="3"/>
-        <v>227.54</v>
-      </c>
-      <c r="AH12" s="2">
-        <f>SUM(O12:R12)</f>
-        <v>180.7</v>
-      </c>
-      <c r="AI12" s="2">
-        <f>SUM(S12:V12)</f>
-        <v>120.461</v>
-      </c>
-      <c r="AJ12" s="2">
-        <f>SUM(W12:Z12)</f>
         <v>94</v>
       </c>
-      <c r="AK12" s="2">
-        <f t="shared" ref="AI12:AO12" si="6">+AJ12*0.9</f>
+      <c r="AO12" s="2">
+        <f t="shared" ref="AO12:AS12" si="9">+AN12*0.9</f>
         <v>84.600000000000009</v>
       </c>
-      <c r="AL12" s="2">
-        <f t="shared" si="6"/>
+      <c r="AP12" s="2">
+        <f t="shared" si="9"/>
         <v>76.140000000000015</v>
       </c>
-      <c r="AM12" s="2">
-        <f t="shared" si="6"/>
+      <c r="AQ12" s="2">
+        <f t="shared" si="9"/>
         <v>68.52600000000001</v>
       </c>
-      <c r="AN12" s="2">
-        <f t="shared" si="6"/>
+      <c r="AR12" s="2">
+        <f t="shared" si="9"/>
         <v>61.673400000000008</v>
       </c>
-      <c r="AO12" s="2">
-        <f t="shared" si="6"/>
+      <c r="AS12" s="2">
+        <f t="shared" si="9"/>
         <v>55.506060000000005</v>
       </c>
     </row>
-    <row r="13" spans="1:41" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:45" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>81</v>
       </c>
@@ -2613,54 +2680,60 @@
         <f>+V13</f>
         <v>48</v>
       </c>
-      <c r="AD13" s="2">
+      <c r="AA13" s="25">
+        <v>47</v>
+      </c>
+      <c r="AB13" s="25"/>
+      <c r="AC13" s="25"/>
+      <c r="AD13" s="25"/>
+      <c r="AH13" s="2">
         <v>72</v>
       </c>
-      <c r="AE13" s="2">
+      <c r="AI13" s="2">
         <v>110.2</v>
       </c>
-      <c r="AF13" s="2">
+      <c r="AJ13" s="2">
+        <f t="shared" si="5"/>
+        <v>127.93200000000002</v>
+      </c>
+      <c r="AK13" s="2">
+        <f t="shared" si="6"/>
+        <v>154.31800000000001</v>
+      </c>
+      <c r="AL13" s="2">
+        <f t="shared" si="1"/>
+        <v>161.80199999999999</v>
+      </c>
+      <c r="AM13" s="2">
         <f t="shared" si="2"/>
-        <v>127.93200000000002</v>
-      </c>
-      <c r="AG13" s="2">
+        <v>169.35599999999999</v>
+      </c>
+      <c r="AN13" s="2">
         <f t="shared" si="3"/>
-        <v>154.31800000000001</v>
-      </c>
-      <c r="AH13" s="2">
-        <f>SUM(O13:R13)</f>
-        <v>161.80199999999999</v>
-      </c>
-      <c r="AI13" s="2">
-        <f>SUM(S13:V13)</f>
-        <v>169.35599999999999</v>
-      </c>
-      <c r="AJ13" s="2">
-        <f>SUM(W13:Z13)</f>
         <v>170.309</v>
       </c>
-      <c r="AK13" s="2">
-        <f t="shared" ref="AK13:AO13" si="7">+AJ13*1.05</f>
+      <c r="AO13" s="2">
+        <f t="shared" ref="AO13:AS13" si="10">+AN13*1.05</f>
         <v>178.82445000000001</v>
       </c>
-      <c r="AL13" s="2">
-        <f t="shared" si="7"/>
+      <c r="AP13" s="2">
+        <f t="shared" si="10"/>
         <v>187.76567250000002</v>
       </c>
-      <c r="AM13" s="2">
-        <f t="shared" si="7"/>
+      <c r="AQ13" s="2">
+        <f t="shared" si="10"/>
         <v>197.15395612500004</v>
       </c>
-      <c r="AN13" s="2">
-        <f t="shared" si="7"/>
+      <c r="AR13" s="2">
+        <f t="shared" si="10"/>
         <v>207.01165393125004</v>
       </c>
-      <c r="AO13" s="2">
-        <f t="shared" si="7"/>
+      <c r="AS13" s="2">
+        <f t="shared" si="10"/>
         <v>217.36223662781254</v>
       </c>
     </row>
-    <row r="14" spans="1:41" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:45" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>82</v>
       </c>
@@ -2735,54 +2808,60 @@
         <f>+V14*1.3</f>
         <v>270.40000000000003</v>
       </c>
-      <c r="AD14" s="2">
+      <c r="AA14" s="25">
+        <v>220</v>
+      </c>
+      <c r="AB14" s="25"/>
+      <c r="AC14" s="25"/>
+      <c r="AD14" s="25"/>
+      <c r="AH14" s="2">
         <v>0</v>
       </c>
-      <c r="AE14" s="2">
+      <c r="AI14" s="2">
         <v>0</v>
       </c>
-      <c r="AF14" s="2">
+      <c r="AJ14" s="2">
+        <f t="shared" si="5"/>
+        <v>5.8999999999999995</v>
+      </c>
+      <c r="AK14" s="2">
+        <f t="shared" si="6"/>
+        <v>169.16300000000001</v>
+      </c>
+      <c r="AL14" s="2">
+        <f t="shared" si="1"/>
+        <v>469.97300000000001</v>
+      </c>
+      <c r="AM14" s="2">
         <f t="shared" si="2"/>
-        <v>5.8999999999999995</v>
-      </c>
-      <c r="AG14" s="2">
+        <v>734.82299999999998</v>
+      </c>
+      <c r="AN14" s="2">
         <f t="shared" si="3"/>
-        <v>169.16300000000001</v>
-      </c>
-      <c r="AH14" s="2">
-        <f>SUM(O14:R14)</f>
-        <v>469.97300000000001</v>
-      </c>
-      <c r="AI14" s="2">
-        <f>SUM(S14:V14)</f>
-        <v>734.82299999999998</v>
-      </c>
-      <c r="AJ14" s="2">
-        <f>SUM(W14:Z14)</f>
         <v>970.49990000000003</v>
-      </c>
-      <c r="AK14" s="2">
-        <f>+AJ14*1.03</f>
-        <v>999.61489700000004</v>
-      </c>
-      <c r="AL14" s="2">
-        <f>+AK14*1.03</f>
-        <v>1029.6033439100001</v>
-      </c>
-      <c r="AM14" s="2">
-        <f>+AL14*1.03</f>
-        <v>1060.4914442273002</v>
-      </c>
-      <c r="AN14" s="2">
-        <f>+AM14*1.03</f>
-        <v>1092.3061875541193</v>
       </c>
       <c r="AO14" s="2">
         <f>+AN14*1.03</f>
+        <v>999.61489700000004</v>
+      </c>
+      <c r="AP14" s="2">
+        <f>+AO14*1.03</f>
+        <v>1029.6033439100001</v>
+      </c>
+      <c r="AQ14" s="2">
+        <f>+AP14*1.03</f>
+        <v>1060.4914442273002</v>
+      </c>
+      <c r="AR14" s="2">
+        <f>+AQ14*1.03</f>
+        <v>1092.3061875541193</v>
+      </c>
+      <c r="AS14" s="2">
+        <f>+AR14*1.03</f>
         <v>1125.0753731807429</v>
       </c>
     </row>
-    <row r="15" spans="1:41" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:45" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
         <v>83</v>
       </c>
@@ -2857,93 +2936,99 @@
         <f>+V15</f>
         <v>39</v>
       </c>
-      <c r="AD15" s="2">
+      <c r="AA15" s="25">
+        <v>37</v>
+      </c>
+      <c r="AB15" s="25"/>
+      <c r="AC15" s="25"/>
+      <c r="AD15" s="25"/>
+      <c r="AH15" s="2">
         <v>97.8</v>
       </c>
-      <c r="AE15" s="2">
+      <c r="AI15" s="2">
         <v>130.1</v>
       </c>
-      <c r="AF15" s="2">
+      <c r="AJ15" s="2">
+        <f t="shared" si="5"/>
+        <v>122.82799999999999</v>
+      </c>
+      <c r="AK15" s="2">
+        <f t="shared" si="6"/>
+        <v>128.37299999999999</v>
+      </c>
+      <c r="AL15" s="2">
+        <f t="shared" si="1"/>
+        <v>131.221</v>
+      </c>
+      <c r="AM15" s="2">
         <f t="shared" si="2"/>
-        <v>122.82799999999999</v>
-      </c>
-      <c r="AG15" s="2">
+        <v>183.82</v>
+      </c>
+      <c r="AN15" s="2">
         <f t="shared" si="3"/>
-        <v>128.37299999999999</v>
-      </c>
-      <c r="AH15" s="2">
-        <f>SUM(O15:R15)</f>
-        <v>131.221</v>
-      </c>
-      <c r="AI15" s="2">
-        <f>SUM(S15:V15)</f>
-        <v>183.82</v>
-      </c>
-      <c r="AJ15" s="2">
-        <f>SUM(W15:Z15)</f>
         <v>197.55799999999999</v>
       </c>
-      <c r="AK15" s="2">
-        <f t="shared" ref="AI15:AO15" si="8">+AJ15*1.03</f>
+      <c r="AO15" s="2">
+        <f t="shared" ref="AO15:AS15" si="11">+AN15*1.03</f>
         <v>203.48473999999999</v>
       </c>
-      <c r="AL15" s="2">
-        <f t="shared" si="8"/>
+      <c r="AP15" s="2">
+        <f t="shared" si="11"/>
         <v>209.58928219999999</v>
       </c>
-      <c r="AM15" s="2">
-        <f t="shared" si="8"/>
+      <c r="AQ15" s="2">
+        <f t="shared" si="11"/>
         <v>215.876960666</v>
       </c>
-      <c r="AN15" s="2">
-        <f t="shared" si="8"/>
+      <c r="AR15" s="2">
+        <f t="shared" si="11"/>
         <v>222.35326948598001</v>
       </c>
-      <c r="AO15" s="2">
-        <f t="shared" si="8"/>
+      <c r="AS15" s="2">
+        <f t="shared" si="11"/>
         <v>229.02386757055942</v>
       </c>
     </row>
-    <row r="16" spans="1:41" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:45" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>63</v>
       </c>
       <c r="C16" s="25"/>
       <c r="D16" s="25"/>
       <c r="E16" s="25">
-        <f t="shared" ref="E16:L16" si="9">SUM(E8:E15)</f>
+        <f t="shared" ref="E16:L16" si="12">SUM(E8:E15)</f>
         <v>460.69999999999993</v>
       </c>
       <c r="F16" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>437</v>
       </c>
       <c r="G16" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>467.8</v>
       </c>
       <c r="H16" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>486.67</v>
       </c>
       <c r="I16" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>393.9</v>
       </c>
       <c r="J16" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>435.2</v>
       </c>
       <c r="K16" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>505.49999999999994</v>
       </c>
       <c r="L16" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>517.66</v>
       </c>
       <c r="M16" s="25">
-        <f t="shared" ref="M16" si="10">SUM(M8:M15)</f>
+        <f t="shared" ref="M16" si="13">SUM(M8:M15)</f>
         <v>493.34800000000001</v>
       </c>
       <c r="N16" s="25"/>
@@ -2959,56 +3044,60 @@
       <c r="X16" s="25"/>
       <c r="Y16" s="25"/>
       <c r="Z16" s="25"/>
-      <c r="AD16" s="2">
-        <f>SUM(AD8:AD15)</f>
+      <c r="AA16" s="25"/>
+      <c r="AB16" s="25"/>
+      <c r="AC16" s="25"/>
+      <c r="AD16" s="25"/>
+      <c r="AH16" s="2">
+        <f>SUM(AH8:AH15)</f>
         <v>1638.6999999999998</v>
       </c>
-      <c r="AE16" s="2">
-        <f>SUM(AE8:AE15)</f>
+      <c r="AI16" s="2">
+        <f>SUM(AI8:AI15)</f>
         <v>1804.7</v>
       </c>
-      <c r="AF16" s="2">
-        <f>SUM(AF8:AF15)</f>
+      <c r="AJ16" s="2">
+        <f>SUM(AJ8:AJ15)</f>
         <v>1783.5700000000002</v>
       </c>
-      <c r="AG16" s="2">
-        <f>SUM(AG8:AG15)</f>
+      <c r="AK16" s="2">
+        <f>SUM(AK8:AK15)</f>
         <v>2042.008</v>
       </c>
-      <c r="AH16" s="2">
-        <f t="shared" ref="AH16:AN16" si="11">SUM(AH8:AH15)</f>
+      <c r="AL16" s="2">
+        <f t="shared" ref="AL16:AR16" si="14">SUM(AL8:AL15)</f>
         <v>2372.5240000000003</v>
       </c>
-      <c r="AI16" s="2">
-        <f t="shared" si="11"/>
+      <c r="AM16" s="2">
+        <f t="shared" si="14"/>
         <v>2808.9549999999999</v>
       </c>
-      <c r="AJ16" s="2">
-        <f t="shared" si="11"/>
+      <c r="AN16" s="2">
+        <f t="shared" si="14"/>
         <v>3133.0028000000002</v>
       </c>
-      <c r="AK16" s="2">
-        <f t="shared" si="11"/>
+      <c r="AO16" s="2">
+        <f t="shared" si="14"/>
         <v>3252.1876239999997</v>
       </c>
-      <c r="AL16" s="2">
-        <f t="shared" si="11"/>
+      <c r="AP16" s="2">
+        <f t="shared" si="14"/>
         <v>3374.7906881400004</v>
       </c>
-      <c r="AM16" s="2">
-        <f t="shared" si="11"/>
+      <c r="AQ16" s="2">
+        <f t="shared" si="14"/>
         <v>3505.5008727320005</v>
       </c>
-      <c r="AN16" s="2">
-        <f t="shared" si="11"/>
+      <c r="AR16" s="2">
+        <f t="shared" si="14"/>
         <v>3644.9441710862229</v>
       </c>
-      <c r="AO16" s="2">
-        <f>SUM(AO8:AO15)</f>
+      <c r="AS16" s="2">
+        <f>SUM(AS8:AS15)</f>
         <v>3788.2510842278398</v>
       </c>
     </row>
-    <row r="17" spans="2:122" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:126" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>62</v>
       </c>
@@ -3083,197 +3172,205 @@
         <f>+V17</f>
         <v>11.679</v>
       </c>
-      <c r="AD17" s="2">
+      <c r="AA17" s="25"/>
+      <c r="AB17" s="25"/>
+      <c r="AC17" s="25"/>
+      <c r="AD17" s="25"/>
+      <c r="AH17" s="2">
         <v>43.005000000000003</v>
       </c>
-      <c r="AE17" s="2">
+      <c r="AI17" s="2">
         <v>54.594000000000001</v>
       </c>
-      <c r="AF17" s="2">
-        <f t="shared" si="2"/>
+      <c r="AJ17" s="2">
+        <f t="shared" si="5"/>
         <v>62.777000000000001</v>
       </c>
-      <c r="AG17" s="2">
-        <f t="shared" si="3"/>
+      <c r="AK17" s="2">
+        <f t="shared" si="6"/>
         <v>54.014000000000003</v>
       </c>
-      <c r="AH17" s="2">
+      <c r="AL17" s="2">
         <f>SUM(O17:R17)</f>
         <v>46.688000000000002</v>
       </c>
-      <c r="AI17" s="2">
+      <c r="AM17" s="2">
         <f>SUM(S17:V17)</f>
         <v>44.47</v>
       </c>
-      <c r="AJ17" s="2">
+      <c r="AN17" s="2">
         <f>SUM(W17:Z17)</f>
         <v>43.953000000000003</v>
       </c>
-      <c r="AK17" s="2">
-        <f t="shared" ref="AI17:AO17" si="12">+AJ17</f>
+      <c r="AO17" s="2">
+        <f t="shared" ref="AO17:AS17" si="15">+AN17</f>
         <v>43.953000000000003</v>
       </c>
-      <c r="AL17" s="2">
-        <f t="shared" si="12"/>
+      <c r="AP17" s="2">
+        <f t="shared" si="15"/>
         <v>43.953000000000003</v>
       </c>
-      <c r="AM17" s="2">
-        <f t="shared" si="12"/>
+      <c r="AQ17" s="2">
+        <f t="shared" si="15"/>
         <v>43.953000000000003</v>
       </c>
-      <c r="AN17" s="2">
-        <f t="shared" si="12"/>
+      <c r="AR17" s="2">
+        <f t="shared" si="15"/>
         <v>43.953000000000003</v>
       </c>
-      <c r="AO17" s="2">
-        <f t="shared" si="12"/>
+      <c r="AS17" s="2">
+        <f t="shared" si="15"/>
         <v>43.953000000000003</v>
       </c>
     </row>
-    <row r="18" spans="2:122" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:126" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
         <v>50</v>
       </c>
       <c r="C18" s="26"/>
       <c r="D18" s="26"/>
       <c r="E18" s="26">
-        <f t="shared" ref="E18:L18" si="13">+E16+E17</f>
+        <f t="shared" ref="E18:L18" si="16">+E16+E17</f>
         <v>476.74299999999994</v>
       </c>
       <c r="F18" s="26">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>452.072</v>
       </c>
       <c r="G18" s="26">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>486.06100000000004</v>
       </c>
       <c r="H18" s="26">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>501.69300000000004</v>
       </c>
       <c r="I18" s="26">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>408.80199999999996</v>
       </c>
       <c r="J18" s="26">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>449.791</v>
       </c>
       <c r="K18" s="26">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>519.33399999999995</v>
       </c>
       <c r="L18" s="26">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>533.798</v>
       </c>
       <c r="M18" s="26">
-        <f t="shared" ref="M18" si="14">+M16+M17</f>
+        <f t="shared" ref="M18" si="17">+M16+M17</f>
         <v>505.34399999999999</v>
       </c>
       <c r="N18" s="26">
-        <f t="shared" ref="N18:Z18" si="15">SUM(N8:N17)</f>
+        <f t="shared" ref="N18:Z18" si="18">SUM(N8:N17)</f>
         <v>537.54600000000005</v>
       </c>
       <c r="O18" s="26">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>596.41500000000008</v>
       </c>
       <c r="P18" s="26">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>595.27499999999998</v>
       </c>
       <c r="Q18" s="26">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>581.36299999999994</v>
       </c>
       <c r="R18" s="26">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>646.15899999999999</v>
       </c>
       <c r="S18" s="26">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>648.84400000000005</v>
       </c>
       <c r="T18" s="26">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>712.02899999999988</v>
       </c>
       <c r="U18" s="26">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>745.87300000000005</v>
       </c>
       <c r="V18" s="26">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>746.67899999999997</v>
       </c>
       <c r="W18" s="26">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>744.50099999999998</v>
       </c>
       <c r="X18" s="26">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>784.95280000000002</v>
       </c>
       <c r="Y18" s="26">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>821.87300000000005</v>
       </c>
       <c r="Z18" s="26">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>825.62900000000002</v>
       </c>
-      <c r="AD18" s="4">
-        <f>+AD16+AD17</f>
+      <c r="AA18" s="26"/>
+      <c r="AB18" s="26"/>
+      <c r="AC18" s="26"/>
+      <c r="AD18" s="26"/>
+      <c r="AH18" s="4">
+        <f>+AH16+AH17</f>
         <v>1681.7049999999999</v>
       </c>
-      <c r="AE18" s="4">
-        <f>+AE16+AE17</f>
+      <c r="AI18" s="4">
+        <f>+AI16+AI17</f>
         <v>1859.2940000000001</v>
       </c>
-      <c r="AF18" s="4">
-        <f>+AF16+AF17</f>
+      <c r="AJ18" s="4">
+        <f>+AJ16+AJ17</f>
         <v>1846.3470000000002</v>
       </c>
-      <c r="AG18" s="4">
-        <f>+AG16+AG17</f>
+      <c r="AK18" s="4">
+        <f>+AK16+AK17</f>
         <v>2096.0219999999999</v>
       </c>
-      <c r="AH18" s="4">
-        <f t="shared" ref="AH18:AO18" si="16">+AH16+AH17</f>
+      <c r="AL18" s="4">
+        <f t="shared" ref="AL18:AS18" si="19">+AL16+AL17</f>
         <v>2419.2120000000004</v>
       </c>
-      <c r="AI18" s="4">
-        <f t="shared" si="16"/>
+      <c r="AM18" s="4">
+        <f t="shared" si="19"/>
         <v>2853.4249999999997</v>
       </c>
-      <c r="AJ18" s="4">
-        <f t="shared" si="16"/>
+      <c r="AN18" s="4">
+        <f t="shared" si="19"/>
         <v>3176.9558000000002</v>
       </c>
-      <c r="AK18" s="4">
-        <f t="shared" si="16"/>
+      <c r="AO18" s="4">
+        <f t="shared" si="19"/>
         <v>3296.1406239999997</v>
       </c>
-      <c r="AL18" s="4">
-        <f t="shared" si="16"/>
+      <c r="AP18" s="4">
+        <f t="shared" si="19"/>
         <v>3418.7436881400004</v>
       </c>
-      <c r="AM18" s="4">
-        <f t="shared" si="16"/>
+      <c r="AQ18" s="4">
+        <f t="shared" si="19"/>
         <v>3549.4538727320005</v>
       </c>
-      <c r="AN18" s="4">
-        <f t="shared" si="16"/>
+      <c r="AR18" s="4">
+        <f t="shared" si="19"/>
         <v>3688.8971710862229</v>
       </c>
-      <c r="AO18" s="4">
-        <f t="shared" si="16"/>
+      <c r="AS18" s="4">
+        <f t="shared" si="19"/>
         <v>3832.2040842278398</v>
       </c>
     </row>
-    <row r="19" spans="2:122" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:126" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
         <v>64</v>
       </c>
@@ -3339,188 +3436,196 @@
       <c r="X19" s="25"/>
       <c r="Y19" s="25"/>
       <c r="Z19" s="25"/>
-      <c r="AD19" s="2">
+      <c r="AA19" s="25"/>
+      <c r="AB19" s="25"/>
+      <c r="AC19" s="25"/>
+      <c r="AD19" s="25"/>
+      <c r="AH19" s="2">
         <v>359.46600000000001</v>
       </c>
-      <c r="AE19" s="2">
+      <c r="AI19" s="2">
         <v>524.27200000000005</v>
       </c>
-      <c r="AF19" s="2">
-        <f t="shared" si="2"/>
+      <c r="AJ19" s="2">
+        <f t="shared" si="5"/>
         <v>470.51499999999999</v>
       </c>
-      <c r="AG19" s="2">
-        <f t="shared" si="3"/>
+      <c r="AK19" s="2">
+        <f t="shared" si="6"/>
         <v>483.66900000000004</v>
       </c>
-      <c r="AH19" s="2">
-        <f>+AH18*0.21</f>
+      <c r="AL19" s="2">
+        <f>+AL18*0.21</f>
         <v>508.0345200000001</v>
       </c>
-      <c r="AI19" s="2">
-        <f t="shared" ref="AI19:AO19" si="17">+AI18*0.21</f>
+      <c r="AM19" s="2">
+        <f t="shared" ref="AM19:AS19" si="20">+AM18*0.21</f>
         <v>599.21924999999987</v>
       </c>
-      <c r="AJ19" s="2">
-        <f t="shared" si="17"/>
+      <c r="AN19" s="2">
+        <f t="shared" si="20"/>
         <v>667.16071799999997</v>
       </c>
-      <c r="AK19" s="2">
-        <f t="shared" si="17"/>
+      <c r="AO19" s="2">
+        <f t="shared" si="20"/>
         <v>692.18953103999991</v>
       </c>
-      <c r="AL19" s="2">
-        <f t="shared" si="17"/>
+      <c r="AP19" s="2">
+        <f t="shared" si="20"/>
         <v>717.93617450940008</v>
       </c>
-      <c r="AM19" s="2">
-        <f t="shared" si="17"/>
+      <c r="AQ19" s="2">
+        <f t="shared" si="20"/>
         <v>745.38531327372004</v>
       </c>
-      <c r="AN19" s="2">
-        <f t="shared" si="17"/>
+      <c r="AR19" s="2">
+        <f t="shared" si="20"/>
         <v>774.66840592810684</v>
       </c>
-      <c r="AO19" s="2">
-        <f t="shared" si="17"/>
+      <c r="AS19" s="2">
+        <f t="shared" si="20"/>
         <v>804.76285768784635</v>
       </c>
     </row>
-    <row r="20" spans="2:122" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:126" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C20" s="25"/>
       <c r="D20" s="25"/>
       <c r="E20" s="25">
-        <f t="shared" ref="E20:L20" si="18">+E18-E19</f>
+        <f t="shared" ref="E20:L20" si="21">+E18-E19</f>
         <v>287.94999999999993</v>
       </c>
       <c r="F20" s="25">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>325.93399999999997</v>
       </c>
       <c r="G20" s="25">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>365.89500000000004</v>
       </c>
       <c r="H20" s="25">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>374.63100000000003</v>
       </c>
       <c r="I20" s="25">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>305.26499999999999</v>
       </c>
       <c r="J20" s="25">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>330.041</v>
       </c>
       <c r="K20" s="25">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>402.36899999999991</v>
       </c>
       <c r="L20" s="25">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>410.67200000000003</v>
       </c>
       <c r="M20" s="25">
-        <f t="shared" ref="M20:W20" si="19">+M18-M19</f>
+        <f t="shared" ref="M20:W20" si="22">+M18-M19</f>
         <v>389.05599999999998</v>
       </c>
       <c r="N20" s="25">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>410.25600000000003</v>
       </c>
       <c r="O20" s="25">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>460.9430000000001</v>
       </c>
       <c r="P20" s="25">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>529.70899999999995</v>
       </c>
       <c r="Q20" s="25">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>456.61799999999994</v>
       </c>
       <c r="R20" s="25">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>510.68099999999998</v>
       </c>
       <c r="S20" s="25">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>523.66399999999999</v>
       </c>
       <c r="T20" s="25">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>581.56999999999994</v>
       </c>
       <c r="U20" s="25">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>557.41600000000005</v>
       </c>
       <c r="V20" s="25">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>610.54</v>
       </c>
       <c r="W20" s="25">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>592.94299999999998</v>
       </c>
       <c r="X20" s="25"/>
       <c r="Y20" s="25"/>
       <c r="Z20" s="25"/>
-      <c r="AD20" s="2">
-        <f>+AD18-AD19</f>
-        <v>1322.239</v>
-      </c>
-      <c r="AE20" s="2">
-        <f>+AE18-AE19</f>
-        <v>1335.0219999999999</v>
-      </c>
-      <c r="AF20" s="2">
-        <f>+AF18-AF19</f>
-        <v>1375.8320000000003</v>
-      </c>
-      <c r="AG20" s="2">
-        <f>+AG18-AG19</f>
-        <v>1612.3529999999998</v>
-      </c>
+      <c r="AA20" s="25"/>
+      <c r="AB20" s="25"/>
+      <c r="AC20" s="25"/>
+      <c r="AD20" s="25"/>
       <c r="AH20" s="2">
         <f>+AH18-AH19</f>
+        <v>1322.239</v>
+      </c>
+      <c r="AI20" s="2">
+        <f>+AI18-AI19</f>
+        <v>1335.0219999999999</v>
+      </c>
+      <c r="AJ20" s="2">
+        <f>+AJ18-AJ19</f>
+        <v>1375.8320000000003</v>
+      </c>
+      <c r="AK20" s="2">
+        <f>+AK18-AK19</f>
+        <v>1612.3529999999998</v>
+      </c>
+      <c r="AL20" s="2">
+        <f>+AL18-AL19</f>
         <v>1911.1774800000003</v>
       </c>
-      <c r="AI20" s="2">
-        <f t="shared" ref="AI20:AO20" si="20">+AI18-AI19</f>
+      <c r="AM20" s="2">
+        <f t="shared" ref="AM20:AS20" si="23">+AM18-AM19</f>
         <v>2254.2057500000001</v>
       </c>
-      <c r="AJ20" s="2">
-        <f t="shared" si="20"/>
+      <c r="AN20" s="2">
+        <f t="shared" si="23"/>
         <v>2509.7950820000001</v>
       </c>
-      <c r="AK20" s="2">
-        <f t="shared" si="20"/>
+      <c r="AO20" s="2">
+        <f t="shared" si="23"/>
         <v>2603.9510929599996</v>
       </c>
-      <c r="AL20" s="2">
-        <f t="shared" si="20"/>
+      <c r="AP20" s="2">
+        <f t="shared" si="23"/>
         <v>2700.8075136306002</v>
       </c>
-      <c r="AM20" s="2">
-        <f t="shared" si="20"/>
+      <c r="AQ20" s="2">
+        <f t="shared" si="23"/>
         <v>2804.0685594582806</v>
       </c>
-      <c r="AN20" s="2">
-        <f t="shared" si="20"/>
+      <c r="AR20" s="2">
+        <f t="shared" si="23"/>
         <v>2914.2287651581159</v>
       </c>
-      <c r="AO20" s="2">
-        <f t="shared" si="20"/>
+      <c r="AS20" s="2">
+        <f t="shared" si="23"/>
         <v>3027.4412265399933</v>
       </c>
     </row>
-    <row r="21" spans="2:122" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:126" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
         <v>68</v>
       </c>
@@ -3586,22 +3691,26 @@
       <c r="X21" s="25"/>
       <c r="Y21" s="25"/>
       <c r="Z21" s="25"/>
-      <c r="AD21" s="2">
+      <c r="AA21" s="25"/>
+      <c r="AB21" s="25"/>
+      <c r="AC21" s="25"/>
+      <c r="AD21" s="25"/>
+      <c r="AH21" s="2">
         <v>715.00699999999995</v>
       </c>
-      <c r="AE21" s="2">
+      <c r="AI21" s="2">
         <v>628.11599999999999</v>
       </c>
-      <c r="AF21" s="2">
-        <f t="shared" si="2"/>
+      <c r="AJ21" s="2">
+        <f t="shared" si="5"/>
         <v>628.79300000000001</v>
       </c>
-      <c r="AG21" s="2">
-        <f t="shared" si="3"/>
+      <c r="AK21" s="2">
+        <f t="shared" si="6"/>
         <v>649.60599999999999</v>
       </c>
     </row>
-    <row r="22" spans="2:122" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:126" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
         <v>69</v>
       </c>
@@ -3667,322 +3776,334 @@
       <c r="X22" s="25"/>
       <c r="Y22" s="25"/>
       <c r="Z22" s="25"/>
-      <c r="AD22" s="2">
+      <c r="AA22" s="25"/>
+      <c r="AB22" s="25"/>
+      <c r="AC22" s="25"/>
+      <c r="AD22" s="25"/>
+      <c r="AH22" s="2">
         <v>680.92399999999998</v>
       </c>
-      <c r="AE22" s="2">
+      <c r="AI22" s="2">
         <v>737.66899999999998</v>
       </c>
-      <c r="AF22" s="2">
-        <f t="shared" si="2"/>
+      <c r="AJ22" s="2">
+        <f t="shared" si="5"/>
         <v>759.375</v>
       </c>
-      <c r="AG22" s="2">
-        <f t="shared" si="3"/>
+      <c r="AK22" s="2">
+        <f t="shared" si="6"/>
         <v>854.00900000000001</v>
       </c>
-      <c r="AH22" s="2">
-        <f>+AG22*1.04</f>
+      <c r="AL22" s="2">
+        <f>+AK22*1.04</f>
         <v>888.1693600000001</v>
       </c>
-      <c r="AI22" s="2">
-        <f t="shared" ref="AI22:AO22" si="21">+AH22*1.04</f>
+      <c r="AM22" s="2">
+        <f t="shared" ref="AM22:AS22" si="24">+AL22*1.04</f>
         <v>923.69613440000012</v>
       </c>
-      <c r="AJ22" s="2">
-        <f t="shared" si="21"/>
+      <c r="AN22" s="2">
+        <f t="shared" si="24"/>
         <v>960.64397977600015</v>
       </c>
-      <c r="AK22" s="2">
-        <f t="shared" si="21"/>
+      <c r="AO22" s="2">
+        <f t="shared" si="24"/>
         <v>999.06973896704017</v>
       </c>
-      <c r="AL22" s="2">
-        <f t="shared" si="21"/>
+      <c r="AP22" s="2">
+        <f t="shared" si="24"/>
         <v>1039.0325285257218</v>
       </c>
-      <c r="AM22" s="2">
-        <f t="shared" si="21"/>
+      <c r="AQ22" s="2">
+        <f t="shared" si="24"/>
         <v>1080.5938296667507</v>
       </c>
-      <c r="AN22" s="2">
-        <f t="shared" si="21"/>
+      <c r="AR22" s="2">
+        <f t="shared" si="24"/>
         <v>1123.8175828534208</v>
       </c>
-      <c r="AO22" s="2">
-        <f t="shared" si="21"/>
+      <c r="AS22" s="2">
+        <f t="shared" si="24"/>
         <v>1168.7702861675577</v>
       </c>
     </row>
-    <row r="23" spans="2:122" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:126" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C23" s="25"/>
       <c r="D23" s="25"/>
       <c r="E23" s="25">
-        <f t="shared" ref="E23:L23" si="22">+E21+E22</f>
+        <f t="shared" ref="E23:L23" si="25">+E21+E22</f>
         <v>326.50299999999999</v>
       </c>
       <c r="F23" s="25">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>352.17899999999997</v>
       </c>
       <c r="G23" s="25">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>323.04300000000001</v>
       </c>
       <c r="H23" s="25">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>345.26800000000003</v>
       </c>
       <c r="I23" s="25">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>341.202</v>
       </c>
       <c r="J23" s="25">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>378.65499999999997</v>
       </c>
       <c r="K23" s="25">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>355.45500000000004</v>
       </c>
       <c r="L23" s="25">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>355.02499999999998</v>
       </c>
       <c r="M23" s="25">
-        <f t="shared" ref="M23:N23" si="23">+M21+M22</f>
+        <f t="shared" ref="M23:N23" si="26">+M21+M22</f>
         <v>374.64499999999998</v>
       </c>
       <c r="N23" s="25">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>418.49</v>
       </c>
       <c r="O23" s="25">
-        <f t="shared" ref="O23:W23" si="24">+O21+O22</f>
+        <f t="shared" ref="O23:W23" si="27">+O21+O22</f>
         <v>382.86900000000003</v>
       </c>
       <c r="P23" s="25">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>383.46600000000001</v>
       </c>
       <c r="Q23" s="25">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>415.24199999999996</v>
       </c>
       <c r="R23" s="25">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>481.274</v>
       </c>
       <c r="S23" s="25">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>430.89300000000003</v>
       </c>
       <c r="T23" s="25">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>446.81899999999996</v>
       </c>
       <c r="U23" s="25">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>438.38099999999997</v>
       </c>
       <c r="V23" s="25">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>440.11599999999999</v>
       </c>
       <c r="W23" s="25">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>364.84699999999998</v>
       </c>
       <c r="X23" s="25"/>
       <c r="Y23" s="25"/>
       <c r="Z23" s="25"/>
-      <c r="AD23" s="2">
-        <f>+AD22+AD21</f>
+      <c r="AA23" s="25"/>
+      <c r="AB23" s="25"/>
+      <c r="AC23" s="25"/>
+      <c r="AD23" s="25"/>
+      <c r="AH23" s="2">
+        <f>+AH22+AH21</f>
         <v>1395.931</v>
       </c>
-      <c r="AE23" s="2">
-        <f>+AE22+AE21</f>
+      <c r="AI23" s="2">
+        <f>+AI22+AI21</f>
         <v>1365.7849999999999</v>
       </c>
-      <c r="AF23" s="2">
-        <f>+AF22+AF21</f>
+      <c r="AJ23" s="2">
+        <f>+AJ22+AJ21</f>
         <v>1388.1680000000001</v>
       </c>
-      <c r="AG23" s="2">
-        <f>+AG22+AG21</f>
+      <c r="AK23" s="2">
+        <f>+AK22+AK21</f>
         <v>1503.615</v>
       </c>
-      <c r="AH23" s="2">
-        <f t="shared" ref="AH23:AO23" si="25">+AH22+AH21</f>
+      <c r="AL23" s="2">
+        <f t="shared" ref="AL23:AS23" si="28">+AL22+AL21</f>
         <v>888.1693600000001</v>
       </c>
-      <c r="AI23" s="2">
-        <f t="shared" si="25"/>
+      <c r="AM23" s="2">
+        <f t="shared" si="28"/>
         <v>923.69613440000012</v>
       </c>
-      <c r="AJ23" s="2">
-        <f t="shared" si="25"/>
+      <c r="AN23" s="2">
+        <f t="shared" si="28"/>
         <v>960.64397977600015</v>
       </c>
-      <c r="AK23" s="2">
-        <f t="shared" si="25"/>
+      <c r="AO23" s="2">
+        <f t="shared" si="28"/>
         <v>999.06973896704017</v>
       </c>
-      <c r="AL23" s="2">
-        <f t="shared" si="25"/>
+      <c r="AP23" s="2">
+        <f t="shared" si="28"/>
         <v>1039.0325285257218</v>
       </c>
-      <c r="AM23" s="2">
-        <f t="shared" si="25"/>
+      <c r="AQ23" s="2">
+        <f t="shared" si="28"/>
         <v>1080.5938296667507</v>
       </c>
-      <c r="AN23" s="2">
-        <f t="shared" si="25"/>
+      <c r="AR23" s="2">
+        <f t="shared" si="28"/>
         <v>1123.8175828534208</v>
       </c>
-      <c r="AO23" s="2">
-        <f t="shared" si="25"/>
+      <c r="AS23" s="2">
+        <f t="shared" si="28"/>
         <v>1168.7702861675577</v>
       </c>
     </row>
-    <row r="24" spans="2:122" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:126" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C24" s="25"/>
       <c r="D24" s="25"/>
       <c r="E24" s="25">
-        <f t="shared" ref="E24:L24" si="26">+E20-E23</f>
+        <f t="shared" ref="E24:L24" si="29">+E20-E23</f>
         <v>-38.553000000000054</v>
       </c>
       <c r="F24" s="25">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-26.245000000000005</v>
       </c>
       <c r="G24" s="25">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>42.852000000000032</v>
       </c>
       <c r="H24" s="25">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>29.363</v>
       </c>
       <c r="I24" s="25">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-35.937000000000012</v>
       </c>
       <c r="J24" s="25">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-48.613999999999976</v>
       </c>
       <c r="K24" s="25">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>46.913999999999874</v>
       </c>
       <c r="L24" s="25">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>55.647000000000048</v>
       </c>
       <c r="M24" s="25">
-        <f t="shared" ref="M24:N24" si="27">+M20-M23</f>
+        <f t="shared" ref="M24:N24" si="30">+M20-M23</f>
         <v>14.411000000000001</v>
       </c>
       <c r="N24" s="25">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-8.2339999999999804</v>
       </c>
       <c r="O24" s="25">
-        <f t="shared" ref="O24:W24" si="28">+O20-O23</f>
+        <f t="shared" ref="O24:W24" si="31">+O20-O23</f>
         <v>78.074000000000069</v>
       </c>
       <c r="P24" s="25">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>146.24299999999994</v>
       </c>
       <c r="Q24" s="25">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>41.375999999999976</v>
       </c>
       <c r="R24" s="25">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>29.406999999999982</v>
       </c>
       <c r="S24" s="25">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>92.770999999999958</v>
       </c>
       <c r="T24" s="25">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>134.75099999999998</v>
       </c>
       <c r="U24" s="25">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>119.03500000000008</v>
       </c>
       <c r="V24" s="25">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>170.42399999999998</v>
       </c>
       <c r="W24" s="25">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>228.096</v>
       </c>
       <c r="X24" s="25"/>
       <c r="Y24" s="25"/>
       <c r="Z24" s="25"/>
-      <c r="AD24" s="2">
-        <f>+AD20-AD23</f>
+      <c r="AA24" s="25"/>
+      <c r="AB24" s="25"/>
+      <c r="AC24" s="25"/>
+      <c r="AD24" s="25"/>
+      <c r="AH24" s="2">
+        <f>+AH20-AH23</f>
         <v>-73.692000000000007</v>
       </c>
-      <c r="AE24" s="2">
-        <f>+AE20-AE23</f>
+      <c r="AI24" s="2">
+        <f>+AI20-AI23</f>
         <v>-30.76299999999992</v>
       </c>
-      <c r="AF24" s="2">
-        <f>+AF20-AF23</f>
+      <c r="AJ24" s="2">
+        <f>+AJ20-AJ23</f>
         <v>-12.335999999999785</v>
       </c>
-      <c r="AG24" s="2">
-        <f>+AG20-AG23</f>
+      <c r="AK24" s="2">
+        <f>+AK20-AK23</f>
         <v>108.73799999999983</v>
       </c>
-      <c r="AH24" s="2">
-        <f t="shared" ref="AH24:AO24" si="29">+AH20-AH23</f>
+      <c r="AL24" s="2">
+        <f t="shared" ref="AL24:AS24" si="32">+AL20-AL23</f>
         <v>1023.0081200000002</v>
       </c>
-      <c r="AI24" s="2">
-        <f t="shared" si="29"/>
+      <c r="AM24" s="2">
+        <f t="shared" si="32"/>
         <v>1330.5096156</v>
       </c>
-      <c r="AJ24" s="2">
-        <f t="shared" si="29"/>
+      <c r="AN24" s="2">
+        <f t="shared" si="32"/>
         <v>1549.1511022239999</v>
       </c>
-      <c r="AK24" s="2">
-        <f t="shared" si="29"/>
+      <c r="AO24" s="2">
+        <f t="shared" si="32"/>
         <v>1604.8813539929595</v>
       </c>
-      <c r="AL24" s="2">
-        <f t="shared" si="29"/>
+      <c r="AP24" s="2">
+        <f t="shared" si="32"/>
         <v>1661.7749851048784</v>
       </c>
-      <c r="AM24" s="2">
-        <f t="shared" si="29"/>
+      <c r="AQ24" s="2">
+        <f t="shared" si="32"/>
         <v>1723.4747297915299</v>
       </c>
-      <c r="AN24" s="2">
-        <f t="shared" si="29"/>
+      <c r="AR24" s="2">
+        <f t="shared" si="32"/>
         <v>1790.4111823046951</v>
       </c>
-      <c r="AO24" s="2">
-        <f t="shared" si="29"/>
+      <c r="AS24" s="2">
+        <f t="shared" si="32"/>
         <v>1858.6709403724356</v>
       </c>
     </row>
-    <row r="25" spans="2:122" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:126" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
         <v>72</v>
       </c>
@@ -4067,190 +4188,198 @@
       <c r="X25" s="25"/>
       <c r="Y25" s="25"/>
       <c r="Z25" s="25"/>
-      <c r="AD25" s="2">
+      <c r="AA25" s="25"/>
+      <c r="AB25" s="25"/>
+      <c r="AC25" s="25"/>
+      <c r="AD25" s="25"/>
+      <c r="AH25" s="2">
         <f>-0.587+22.748-23.46+6.945</f>
         <v>5.6460000000000008</v>
       </c>
-      <c r="AE25" s="2">
+      <c r="AI25" s="2">
         <f>16.61-29.309+7.142</f>
         <v>-5.5570000000000013</v>
       </c>
-      <c r="AF25" s="2">
-        <f t="shared" ref="AF25" si="30">SUM(G25:J25)</f>
+      <c r="AJ25" s="2">
+        <f t="shared" ref="AJ25" si="33">SUM(G25:J25)</f>
         <v>6.9910000000000014</v>
       </c>
-      <c r="AG25" s="2">
-        <f t="shared" ref="AG25:AG27" si="31">SUM(K25:N25)</f>
+      <c r="AK25" s="2">
+        <f t="shared" ref="AK25:AK27" si="34">SUM(K25:N25)</f>
         <v>1.4000000000001123E-2</v>
       </c>
-      <c r="AH25" s="2">
-        <f>+AG38*$AR$36</f>
+      <c r="AL25" s="2">
+        <f>+AK38*$AV$36</f>
         <v>0</v>
       </c>
-      <c r="AI25" s="2">
-        <f t="shared" ref="AI25:AO25" si="32">+AH38*$AR$36</f>
+      <c r="AM25" s="2">
+        <f t="shared" ref="AM25:AS25" si="35">+AL38*$AV$36</f>
         <v>20.460162400000005</v>
       </c>
-      <c r="AJ25" s="2">
-        <f t="shared" si="32"/>
+      <c r="AN25" s="2">
+        <f t="shared" si="35"/>
         <v>47.479557960000001</v>
       </c>
-      <c r="AK25" s="2">
-        <f t="shared" si="32"/>
+      <c r="AO25" s="2">
+        <f t="shared" si="35"/>
         <v>76.218909843311991</v>
       </c>
-      <c r="AL25" s="2">
-        <f t="shared" si="32"/>
+      <c r="AP25" s="2">
+        <f t="shared" si="35"/>
         <v>103.11651406469235</v>
       </c>
-      <c r="AM25" s="2">
-        <f t="shared" si="32"/>
+      <c r="AQ25" s="2">
+        <f t="shared" si="35"/>
         <v>131.35477805140548</v>
       </c>
-      <c r="AN25" s="2">
-        <f t="shared" si="32"/>
+      <c r="AR25" s="2">
+        <f t="shared" si="35"/>
         <v>161.03205017689245</v>
       </c>
-      <c r="AO25" s="2">
-        <f t="shared" si="32"/>
+      <c r="AS25" s="2">
+        <f t="shared" si="35"/>
         <v>192.25514189659785</v>
       </c>
     </row>
-    <row r="26" spans="2:122" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:126" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
       <c r="E26" s="25">
-        <f t="shared" ref="E26:W26" si="33">+E24+E25</f>
+        <f t="shared" ref="E26:W26" si="36">+E24+E25</f>
         <v>-43.828000000000053</v>
       </c>
       <c r="F26" s="25">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>-21.590000000000003</v>
       </c>
       <c r="G26" s="25">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>40.994000000000035</v>
       </c>
       <c r="H26" s="25">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>31.847000000000001</v>
       </c>
       <c r="I26" s="25">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>-28.878000000000011</v>
       </c>
       <c r="J26" s="25">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>-49.307999999999979</v>
       </c>
       <c r="K26" s="25">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>43.773999999999873</v>
       </c>
       <c r="L26" s="25">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>51.346000000000046</v>
       </c>
       <c r="M26" s="25">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>14.924000000000001</v>
       </c>
       <c r="N26" s="25">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>-1.2919999999999785</v>
       </c>
       <c r="O26" s="25">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>72.427000000000064</v>
       </c>
       <c r="P26" s="25">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>151.48699999999994</v>
       </c>
       <c r="Q26" s="25">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>57.383999999999972</v>
       </c>
       <c r="R26" s="25">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>34.514999999999986</v>
       </c>
       <c r="S26" s="25">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>109.85599999999995</v>
       </c>
       <c r="T26" s="25">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>146.43499999999997</v>
       </c>
       <c r="U26" s="25">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>134.12000000000009</v>
       </c>
       <c r="V26" s="25">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>185.52699999999999</v>
       </c>
       <c r="W26" s="25">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>244.24600000000001</v>
       </c>
       <c r="X26" s="25"/>
       <c r="Y26" s="25"/>
       <c r="Z26" s="25"/>
-      <c r="AD26" s="2">
-        <f>+AD24+AD25</f>
+      <c r="AA26" s="25"/>
+      <c r="AB26" s="25"/>
+      <c r="AC26" s="25"/>
+      <c r="AD26" s="25"/>
+      <c r="AH26" s="2">
+        <f>+AH24+AH25</f>
         <v>-68.046000000000006</v>
       </c>
-      <c r="AE26" s="2">
-        <f>+AE24+AE25</f>
+      <c r="AI26" s="2">
+        <f>+AI24+AI25</f>
         <v>-36.319999999999922</v>
       </c>
-      <c r="AF26" s="2">
-        <f>+AF24+AF25</f>
+      <c r="AJ26" s="2">
+        <f>+AJ24+AJ25</f>
         <v>-5.3449999999997839</v>
       </c>
-      <c r="AG26" s="2">
-        <f>+AG24+AG25</f>
+      <c r="AK26" s="2">
+        <f>+AK24+AK25</f>
         <v>108.75199999999982</v>
       </c>
-      <c r="AH26" s="2">
-        <f t="shared" ref="AH26:AO26" si="34">+AH24+AH25</f>
+      <c r="AL26" s="2">
+        <f t="shared" ref="AL26:AS26" si="37">+AL24+AL25</f>
         <v>1023.0081200000002</v>
       </c>
-      <c r="AI26" s="2">
-        <f t="shared" si="34"/>
+      <c r="AM26" s="2">
+        <f t="shared" si="37"/>
         <v>1350.9697779999999</v>
       </c>
-      <c r="AJ26" s="2">
-        <f t="shared" si="34"/>
+      <c r="AN26" s="2">
+        <f t="shared" si="37"/>
         <v>1596.6306601839999</v>
       </c>
-      <c r="AK26" s="2">
-        <f t="shared" si="34"/>
+      <c r="AO26" s="2">
+        <f t="shared" si="37"/>
         <v>1681.1002638362716</v>
       </c>
-      <c r="AL26" s="2">
-        <f t="shared" si="34"/>
+      <c r="AP26" s="2">
+        <f t="shared" si="37"/>
         <v>1764.8914991695708</v>
       </c>
-      <c r="AM26" s="2">
-        <f t="shared" si="34"/>
+      <c r="AQ26" s="2">
+        <f t="shared" si="37"/>
         <v>1854.8295078429353</v>
       </c>
-      <c r="AN26" s="2">
-        <f t="shared" si="34"/>
+      <c r="AR26" s="2">
+        <f t="shared" si="37"/>
         <v>1951.4432324815875</v>
       </c>
-      <c r="AO26" s="2">
-        <f t="shared" si="34"/>
+      <c r="AS26" s="2">
+        <f t="shared" si="37"/>
         <v>2050.9260822690335</v>
       </c>
     </row>
-    <row r="27" spans="2:122" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:126" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
         <v>74</v>
       </c>
@@ -4316,125 +4445,129 @@
       <c r="X27" s="25"/>
       <c r="Y27" s="25"/>
       <c r="Z27" s="25"/>
-      <c r="AD27" s="2">
+      <c r="AA27" s="25"/>
+      <c r="AB27" s="25"/>
+      <c r="AC27" s="25"/>
+      <c r="AD27" s="25"/>
+      <c r="AH27" s="2">
         <v>0</v>
       </c>
-      <c r="AE27" s="2">
+      <c r="AI27" s="2">
         <v>0</v>
       </c>
-      <c r="AF27" s="2">
-        <f t="shared" ref="AF27" si="35">SUM(G27:J27)</f>
+      <c r="AJ27" s="2">
+        <f t="shared" ref="AJ27" si="38">SUM(G27:J27)</f>
         <v>-11.27</v>
       </c>
-      <c r="AG27" s="2">
-        <f t="shared" si="31"/>
+      <c r="AK27" s="2">
+        <f t="shared" si="34"/>
         <v>8.0150000000000006</v>
       </c>
-      <c r="AH27" s="2">
-        <f>+AH26*0</f>
+      <c r="AL27" s="2">
+        <f>+AL26*0</f>
         <v>0</v>
       </c>
-      <c r="AI27" s="2">
-        <f>+AI26*0</f>
+      <c r="AM27" s="2">
+        <f>+AM26*0</f>
         <v>0</v>
       </c>
-      <c r="AJ27" s="2">
-        <f>+AJ26*0.1</f>
+      <c r="AN27" s="2">
+        <f>+AN26*0.1</f>
         <v>159.6630660184</v>
       </c>
-      <c r="AK27" s="2">
-        <f>+AK26*0.2</f>
+      <c r="AO27" s="2">
+        <f>+AO26*0.2</f>
         <v>336.22005276725434</v>
       </c>
-      <c r="AL27" s="2">
-        <f t="shared" ref="AL27:AO27" si="36">+AL26*0.2</f>
+      <c r="AP27" s="2">
+        <f t="shared" ref="AP27:AS27" si="39">+AP26*0.2</f>
         <v>352.97829983391421</v>
       </c>
-      <c r="AM27" s="2">
-        <f t="shared" si="36"/>
+      <c r="AQ27" s="2">
+        <f t="shared" si="39"/>
         <v>370.96590156858707</v>
       </c>
-      <c r="AN27" s="2">
-        <f t="shared" si="36"/>
+      <c r="AR27" s="2">
+        <f t="shared" si="39"/>
         <v>390.28864649631754</v>
       </c>
-      <c r="AO27" s="2">
-        <f t="shared" si="36"/>
+      <c r="AS27" s="2">
+        <f t="shared" si="39"/>
         <v>410.18521645380673</v>
       </c>
     </row>
-    <row r="28" spans="2:122" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:126" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B28" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C28" s="25"/>
       <c r="D28" s="25"/>
       <c r="E28" s="25">
-        <f t="shared" ref="E28:U28" si="37">+E26-E27</f>
+        <f t="shared" ref="E28:U28" si="40">+E26-E27</f>
         <v>-43.828000000000053</v>
       </c>
       <c r="F28" s="25">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>-21.590000000000003</v>
       </c>
       <c r="G28" s="25">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>35.137000000000036</v>
       </c>
       <c r="H28" s="25">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>30.632000000000001</v>
       </c>
       <c r="I28" s="25">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>-19.21200000000001</v>
       </c>
       <c r="J28" s="25">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>-40.631999999999977</v>
       </c>
       <c r="K28" s="25">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>30.384999999999874</v>
       </c>
       <c r="L28" s="25">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>44.159000000000049</v>
       </c>
       <c r="M28" s="25">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>10.176000000000002</v>
       </c>
       <c r="N28" s="25">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>16.017000000000024</v>
       </c>
       <c r="O28" s="25">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>66.522000000000062</v>
       </c>
       <c r="P28" s="25">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>136.71699999999993</v>
       </c>
       <c r="Q28" s="25">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>56.092999999999975</v>
       </c>
       <c r="R28" s="25">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>35.562999999999988</v>
       </c>
       <c r="S28" s="25">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>92.970999999999947</v>
       </c>
       <c r="T28" s="25">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>121.47299999999997</v>
       </c>
       <c r="U28" s="25">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>105.75900000000009</v>
       </c>
       <c r="V28" s="25">
@@ -4448,512 +4581,520 @@
       <c r="X28" s="25"/>
       <c r="Y28" s="25"/>
       <c r="Z28" s="25"/>
-      <c r="AD28" s="2">
-        <f>+AD26-AD27</f>
+      <c r="AA28" s="25"/>
+      <c r="AB28" s="25"/>
+      <c r="AC28" s="25"/>
+      <c r="AD28" s="25"/>
+      <c r="AH28" s="2">
+        <f>+AH26-AH27</f>
         <v>-68.046000000000006</v>
       </c>
-      <c r="AE28" s="2">
-        <f>+AE26-AE27</f>
+      <c r="AI28" s="2">
+        <f>+AI26-AI27</f>
         <v>-36.319999999999922</v>
       </c>
-      <c r="AF28" s="2">
-        <f>+AF26-AF27</f>
+      <c r="AJ28" s="2">
+        <f>+AJ26-AJ27</f>
         <v>5.9250000000002156</v>
       </c>
-      <c r="AG28" s="2">
-        <f>+AG26-AG27</f>
+      <c r="AK28" s="2">
+        <f>+AK26-AK27</f>
         <v>100.73699999999982</v>
       </c>
-      <c r="AH28" s="2">
-        <f t="shared" ref="AH28:AO28" si="38">+AH26-AH27</f>
+      <c r="AL28" s="2">
+        <f t="shared" ref="AL28:AS28" si="41">+AL26-AL27</f>
         <v>1023.0081200000002</v>
       </c>
-      <c r="AI28" s="2">
-        <f t="shared" si="38"/>
+      <c r="AM28" s="2">
+        <f t="shared" si="41"/>
         <v>1350.9697779999999</v>
       </c>
-      <c r="AJ28" s="2">
-        <f t="shared" si="38"/>
+      <c r="AN28" s="2">
+        <f t="shared" si="41"/>
         <v>1436.9675941655998</v>
       </c>
-      <c r="AK28" s="2">
-        <f t="shared" si="38"/>
+      <c r="AO28" s="2">
+        <f t="shared" si="41"/>
         <v>1344.8802110690172</v>
       </c>
-      <c r="AL28" s="2">
-        <f t="shared" si="38"/>
+      <c r="AP28" s="2">
+        <f t="shared" si="41"/>
         <v>1411.9131993356566</v>
       </c>
-      <c r="AM28" s="2">
-        <f t="shared" si="38"/>
+      <c r="AQ28" s="2">
+        <f t="shared" si="41"/>
         <v>1483.8636062743483</v>
       </c>
-      <c r="AN28" s="2">
-        <f t="shared" si="38"/>
+      <c r="AR28" s="2">
+        <f t="shared" si="41"/>
         <v>1561.1545859852699</v>
       </c>
-      <c r="AO28" s="2">
-        <f t="shared" si="38"/>
+      <c r="AS28" s="2">
+        <f t="shared" si="41"/>
         <v>1640.7408658152267</v>
       </c>
-      <c r="AP28" s="2">
-        <f>+AO28*(1+$AR$35)</f>
+      <c r="AT28" s="2">
+        <f>+AS28*(1+$AV$35)</f>
         <v>1624.3334571570745</v>
       </c>
-      <c r="AQ28" s="2">
-        <f t="shared" ref="AQ28:DB28" si="39">+AP28*(1+$AR$35)</f>
+      <c r="AU28" s="2">
+        <f t="shared" ref="AU28:DF28" si="42">+AT28*(1+$AV$35)</f>
         <v>1608.0901225855037</v>
       </c>
-      <c r="AR28" s="2">
-        <f t="shared" si="39"/>
+      <c r="AV28" s="2">
+        <f t="shared" si="42"/>
         <v>1592.0092213596486</v>
       </c>
-      <c r="AS28" s="2">
-        <f t="shared" si="39"/>
+      <c r="AW28" s="2">
+        <f t="shared" si="42"/>
         <v>1576.0891291460521</v>
       </c>
-      <c r="AT28" s="2">
-        <f t="shared" si="39"/>
+      <c r="AX28" s="2">
+        <f t="shared" si="42"/>
         <v>1560.3282378545916</v>
       </c>
-      <c r="AU28" s="2">
-        <f t="shared" si="39"/>
+      <c r="AY28" s="2">
+        <f t="shared" si="42"/>
         <v>1544.7249554760458</v>
       </c>
-      <c r="AV28" s="2">
-        <f t="shared" si="39"/>
+      <c r="AZ28" s="2">
+        <f t="shared" si="42"/>
         <v>1529.2777059212854</v>
       </c>
-      <c r="AW28" s="2">
-        <f t="shared" si="39"/>
+      <c r="BA28" s="2">
+        <f t="shared" si="42"/>
         <v>1513.9849288620726</v>
       </c>
-      <c r="AX28" s="2">
-        <f t="shared" si="39"/>
+      <c r="BB28" s="2">
+        <f t="shared" si="42"/>
         <v>1498.8450795734518</v>
       </c>
-      <c r="AY28" s="2">
-        <f t="shared" si="39"/>
+      <c r="BC28" s="2">
+        <f t="shared" si="42"/>
         <v>1483.8566287777173</v>
       </c>
-      <c r="AZ28" s="2">
-        <f t="shared" si="39"/>
+      <c r="BD28" s="2">
+        <f t="shared" si="42"/>
         <v>1469.0180624899401</v>
       </c>
-      <c r="BA28" s="2">
-        <f t="shared" si="39"/>
+      <c r="BE28" s="2">
+        <f t="shared" si="42"/>
         <v>1454.3278818650408</v>
       </c>
-      <c r="BB28" s="2">
-        <f t="shared" si="39"/>
+      <c r="BF28" s="2">
+        <f t="shared" si="42"/>
         <v>1439.7846030463904</v>
       </c>
-      <c r="BC28" s="2">
-        <f t="shared" si="39"/>
+      <c r="BG28" s="2">
+        <f t="shared" si="42"/>
         <v>1425.3867570159266</v>
       </c>
-      <c r="BD28" s="2">
-        <f t="shared" si="39"/>
+      <c r="BH28" s="2">
+        <f t="shared" si="42"/>
         <v>1411.1328894457674</v>
       </c>
-      <c r="BE28" s="2">
-        <f t="shared" si="39"/>
+      <c r="BI28" s="2">
+        <f t="shared" si="42"/>
         <v>1397.0215605513097</v>
       </c>
-      <c r="BF28" s="2">
-        <f t="shared" si="39"/>
+      <c r="BJ28" s="2">
+        <f t="shared" si="42"/>
         <v>1383.0513449457965</v>
       </c>
-      <c r="BG28" s="2">
-        <f t="shared" si="39"/>
+      <c r="BK28" s="2">
+        <f t="shared" si="42"/>
         <v>1369.2208314963384</v>
       </c>
-      <c r="BH28" s="2">
-        <f t="shared" si="39"/>
+      <c r="BL28" s="2">
+        <f t="shared" si="42"/>
         <v>1355.528623181375</v>
       </c>
-      <c r="BI28" s="2">
-        <f t="shared" si="39"/>
+      <c r="BM28" s="2">
+        <f t="shared" si="42"/>
         <v>1341.9733369495611</v>
       </c>
-      <c r="BJ28" s="2">
-        <f t="shared" si="39"/>
+      <c r="BN28" s="2">
+        <f t="shared" si="42"/>
         <v>1328.5536035800656</v>
       </c>
-      <c r="BK28" s="2">
-        <f t="shared" si="39"/>
+      <c r="BO28" s="2">
+        <f t="shared" si="42"/>
         <v>1315.2680675442648</v>
       </c>
-      <c r="BL28" s="2">
-        <f t="shared" si="39"/>
+      <c r="BP28" s="2">
+        <f t="shared" si="42"/>
         <v>1302.115386868822</v>
       </c>
-      <c r="BM28" s="2">
-        <f t="shared" si="39"/>
+      <c r="BQ28" s="2">
+        <f t="shared" si="42"/>
         <v>1289.0942330001337</v>
       </c>
-      <c r="BN28" s="2">
-        <f t="shared" si="39"/>
+      <c r="BR28" s="2">
+        <f t="shared" si="42"/>
         <v>1276.2032906701324</v>
       </c>
-      <c r="BO28" s="2">
-        <f t="shared" si="39"/>
+      <c r="BS28" s="2">
+        <f t="shared" si="42"/>
         <v>1263.4412577634312</v>
       </c>
-      <c r="BP28" s="2">
-        <f t="shared" si="39"/>
+      <c r="BT28" s="2">
+        <f t="shared" si="42"/>
         <v>1250.8068451857969</v>
       </c>
-      <c r="BQ28" s="2">
-        <f t="shared" si="39"/>
+      <c r="BU28" s="2">
+        <f t="shared" si="42"/>
         <v>1238.2987767339389</v>
       </c>
-      <c r="BR28" s="2">
-        <f t="shared" si="39"/>
+      <c r="BV28" s="2">
+        <f t="shared" si="42"/>
         <v>1225.9157889665994</v>
       </c>
-      <c r="BS28" s="2">
-        <f t="shared" si="39"/>
+      <c r="BW28" s="2">
+        <f t="shared" si="42"/>
         <v>1213.6566310769333</v>
       </c>
-      <c r="BT28" s="2">
-        <f t="shared" si="39"/>
+      <c r="BX28" s="2">
+        <f t="shared" si="42"/>
         <v>1201.5200647661641</v>
       </c>
-      <c r="BU28" s="2">
-        <f t="shared" si="39"/>
+      <c r="BY28" s="2">
+        <f t="shared" si="42"/>
         <v>1189.5048641185024</v>
       </c>
-      <c r="BV28" s="2">
-        <f t="shared" si="39"/>
+      <c r="BZ28" s="2">
+        <f t="shared" si="42"/>
         <v>1177.6098154773174</v>
       </c>
-      <c r="BW28" s="2">
-        <f t="shared" si="39"/>
+      <c r="CA28" s="2">
+        <f t="shared" si="42"/>
         <v>1165.8337173225443</v>
       </c>
-      <c r="BX28" s="2">
-        <f t="shared" si="39"/>
+      <c r="CB28" s="2">
+        <f t="shared" si="42"/>
         <v>1154.1753801493189</v>
       </c>
-      <c r="BY28" s="2">
-        <f t="shared" si="39"/>
+      <c r="CC28" s="2">
+        <f t="shared" si="42"/>
         <v>1142.6336263478258</v>
       </c>
-      <c r="BZ28" s="2">
-        <f t="shared" si="39"/>
+      <c r="CD28" s="2">
+        <f t="shared" si="42"/>
         <v>1131.2072900843475</v>
       </c>
-      <c r="CA28" s="2">
-        <f t="shared" si="39"/>
+      <c r="CE28" s="2">
+        <f t="shared" si="42"/>
         <v>1119.895217183504</v>
       </c>
-      <c r="CB28" s="2">
-        <f t="shared" si="39"/>
+      <c r="CF28" s="2">
+        <f t="shared" si="42"/>
         <v>1108.6962650116689</v>
       </c>
-      <c r="CC28" s="2">
-        <f t="shared" si="39"/>
+      <c r="CG28" s="2">
+        <f t="shared" si="42"/>
         <v>1097.6093023615522</v>
       </c>
-      <c r="CD28" s="2">
-        <f t="shared" si="39"/>
+      <c r="CH28" s="2">
+        <f t="shared" si="42"/>
         <v>1086.6332093379367</v>
       </c>
-      <c r="CE28" s="2">
-        <f t="shared" si="39"/>
+      <c r="CI28" s="2">
+        <f t="shared" si="42"/>
         <v>1075.7668772445572</v>
       </c>
-      <c r="CF28" s="2">
-        <f t="shared" si="39"/>
+      <c r="CJ28" s="2">
+        <f t="shared" si="42"/>
         <v>1065.0092084721116</v>
       </c>
-      <c r="CG28" s="2">
-        <f t="shared" si="39"/>
+      <c r="CK28" s="2">
+        <f t="shared" si="42"/>
         <v>1054.3591163873905</v>
       </c>
-      <c r="CH28" s="2">
-        <f t="shared" si="39"/>
+      <c r="CL28" s="2">
+        <f t="shared" si="42"/>
         <v>1043.8155252235165</v>
       </c>
-      <c r="CI28" s="2">
-        <f t="shared" si="39"/>
+      <c r="CM28" s="2">
+        <f t="shared" si="42"/>
         <v>1033.3773699712813</v>
       </c>
-      <c r="CJ28" s="2">
-        <f t="shared" si="39"/>
+      <c r="CN28" s="2">
+        <f t="shared" si="42"/>
         <v>1023.0435962715684</v>
       </c>
-      <c r="CK28" s="2">
-        <f t="shared" si="39"/>
+      <c r="CO28" s="2">
+        <f t="shared" si="42"/>
         <v>1012.8131603088527</v>
       </c>
-      <c r="CL28" s="2">
-        <f t="shared" si="39"/>
+      <c r="CP28" s="2">
+        <f t="shared" si="42"/>
         <v>1002.6850287057642</v>
       </c>
-      <c r="CM28" s="2">
-        <f t="shared" si="39"/>
+      <c r="CQ28" s="2">
+        <f t="shared" si="42"/>
         <v>992.6581784187066</v>
       </c>
-      <c r="CN28" s="2">
-        <f t="shared" si="39"/>
+      <c r="CR28" s="2">
+        <f t="shared" si="42"/>
         <v>982.73159663451952</v>
       </c>
-      <c r="CO28" s="2">
-        <f t="shared" si="39"/>
+      <c r="CS28" s="2">
+        <f t="shared" si="42"/>
         <v>972.90428066817435</v>
       </c>
-      <c r="CP28" s="2">
-        <f t="shared" si="39"/>
+      <c r="CT28" s="2">
+        <f t="shared" si="42"/>
         <v>963.17523786149263</v>
       </c>
-      <c r="CQ28" s="2">
-        <f t="shared" si="39"/>
+      <c r="CU28" s="2">
+        <f t="shared" si="42"/>
         <v>953.54348548287771</v>
       </c>
-      <c r="CR28" s="2">
-        <f t="shared" si="39"/>
+      <c r="CV28" s="2">
+        <f t="shared" si="42"/>
         <v>944.00805062804898</v>
       </c>
-      <c r="CS28" s="2">
-        <f t="shared" si="39"/>
+      <c r="CW28" s="2">
+        <f t="shared" si="42"/>
         <v>934.56797012176844</v>
       </c>
-      <c r="CT28" s="2">
-        <f t="shared" si="39"/>
+      <c r="CX28" s="2">
+        <f t="shared" si="42"/>
         <v>925.22229042055073</v>
       </c>
-      <c r="CU28" s="2">
-        <f t="shared" si="39"/>
+      <c r="CY28" s="2">
+        <f t="shared" si="42"/>
         <v>915.97006751634524</v>
       </c>
-      <c r="CV28" s="2">
-        <f t="shared" si="39"/>
+      <c r="CZ28" s="2">
+        <f t="shared" si="42"/>
         <v>906.8103668411818</v>
       </c>
-      <c r="CW28" s="2">
-        <f t="shared" si="39"/>
+      <c r="DA28" s="2">
+        <f t="shared" si="42"/>
         <v>897.74226317276998</v>
       </c>
-      <c r="CX28" s="2">
-        <f t="shared" si="39"/>
+      <c r="DB28" s="2">
+        <f t="shared" si="42"/>
         <v>888.7648405410423</v>
       </c>
-      <c r="CY28" s="2">
-        <f t="shared" si="39"/>
+      <c r="DC28" s="2">
+        <f t="shared" si="42"/>
         <v>879.87719213563184</v>
       </c>
-      <c r="CZ28" s="2">
-        <f t="shared" si="39"/>
+      <c r="DD28" s="2">
+        <f t="shared" si="42"/>
         <v>871.07842021427552</v>
       </c>
-      <c r="DA28" s="2">
-        <f t="shared" si="39"/>
+      <c r="DE28" s="2">
+        <f t="shared" si="42"/>
         <v>862.36763601213272</v>
       </c>
-      <c r="DB28" s="2">
-        <f t="shared" si="39"/>
+      <c r="DF28" s="2">
+        <f t="shared" si="42"/>
         <v>853.74395965201143</v>
       </c>
-      <c r="DC28" s="2">
-        <f t="shared" ref="DC28:DR28" si="40">+DB28*(1+$AR$35)</f>
+      <c r="DG28" s="2">
+        <f t="shared" ref="DG28:DV28" si="43">+DF28*(1+$AV$35)</f>
         <v>845.2065200554913</v>
       </c>
-      <c r="DD28" s="2">
-        <f t="shared" si="40"/>
+      <c r="DH28" s="2">
+        <f t="shared" si="43"/>
         <v>836.7544548549364</v>
       </c>
-      <c r="DE28" s="2">
-        <f t="shared" si="40"/>
+      <c r="DI28" s="2">
+        <f t="shared" si="43"/>
         <v>828.38691030638699</v>
       </c>
-      <c r="DF28" s="2">
-        <f t="shared" si="40"/>
+      <c r="DJ28" s="2">
+        <f t="shared" si="43"/>
         <v>820.10304120332307</v>
       </c>
-      <c r="DG28" s="2">
-        <f t="shared" si="40"/>
+      <c r="DK28" s="2">
+        <f t="shared" si="43"/>
         <v>811.90201079128985</v>
       </c>
-      <c r="DH28" s="2">
-        <f t="shared" si="40"/>
+      <c r="DL28" s="2">
+        <f t="shared" si="43"/>
         <v>803.78299068337697</v>
       </c>
-      <c r="DI28" s="2">
-        <f t="shared" si="40"/>
+      <c r="DM28" s="2">
+        <f t="shared" si="43"/>
         <v>795.74516077654323</v>
       </c>
-      <c r="DJ28" s="2">
-        <f t="shared" si="40"/>
+      <c r="DN28" s="2">
+        <f t="shared" si="43"/>
         <v>787.78770916877784</v>
       </c>
-      <c r="DK28" s="2">
-        <f t="shared" si="40"/>
+      <c r="DO28" s="2">
+        <f t="shared" si="43"/>
         <v>779.90983207709007</v>
       </c>
-      <c r="DL28" s="2">
-        <f t="shared" si="40"/>
+      <c r="DP28" s="2">
+        <f t="shared" si="43"/>
         <v>772.11073375631918</v>
       </c>
-      <c r="DM28" s="2">
-        <f t="shared" si="40"/>
+      <c r="DQ28" s="2">
+        <f t="shared" si="43"/>
         <v>764.38962641875594</v>
       </c>
-      <c r="DN28" s="2">
-        <f t="shared" si="40"/>
+      <c r="DR28" s="2">
+        <f t="shared" si="43"/>
         <v>756.74573015456838</v>
       </c>
-      <c r="DO28" s="2">
-        <f t="shared" si="40"/>
+      <c r="DS28" s="2">
+        <f t="shared" si="43"/>
         <v>749.17827285302269</v>
       </c>
-      <c r="DP28" s="2">
-        <f t="shared" si="40"/>
+      <c r="DT28" s="2">
+        <f t="shared" si="43"/>
         <v>741.68649012449248</v>
       </c>
-      <c r="DQ28" s="2">
-        <f t="shared" si="40"/>
+      <c r="DU28" s="2">
+        <f t="shared" si="43"/>
         <v>734.26962522324754</v>
       </c>
-      <c r="DR28" s="2">
-        <f t="shared" si="40"/>
+      <c r="DV28" s="2">
+        <f t="shared" si="43"/>
         <v>726.92692897101506</v>
       </c>
     </row>
-    <row r="29" spans="2:122" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:126" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>70</v>
       </c>
       <c r="E29" s="27">
-        <f t="shared" ref="E29:Q29" si="41">+E28/E30</f>
+        <f t="shared" ref="E29:Q29" si="44">+E28/E30</f>
         <v>-0.22171858716877307</v>
       </c>
       <c r="F29" s="27">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>-0.11703419414991655</v>
       </c>
       <c r="G29" s="27">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>0.19058389607571954</v>
       </c>
       <c r="H29" s="27">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>0.16519708564556404</v>
       </c>
       <c r="I29" s="27">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>-0.10486098223934857</v>
       </c>
       <c r="J29" s="27">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>-0.22136265077306938</v>
       </c>
       <c r="K29" s="27">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>0.15591166117627678</v>
       </c>
       <c r="L29" s="27">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>0.23558000085357031</v>
       </c>
       <c r="M29" s="27">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>5.4828472442981308E-2</v>
       </c>
       <c r="N29" s="27">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>8.6099941944223587E-2</v>
       </c>
       <c r="O29" s="27">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>0.34225649943662151</v>
       </c>
       <c r="P29" s="27">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>0.70112001148729697</v>
       </c>
       <c r="Q29" s="27">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>0.29341486506985803</v>
       </c>
       <c r="R29" s="27">
-        <f>R28/R30</f>
+        <f t="shared" ref="R29:W29" si="45">R28/R30</f>
         <v>0.1853803730230715</v>
       </c>
       <c r="S29" s="27">
-        <f>S28/S30</f>
+        <f t="shared" si="45"/>
         <v>0.46657666790456759</v>
       </c>
       <c r="T29" s="27">
-        <f>T28/T30</f>
+        <f t="shared" si="45"/>
         <v>0.60583526595346737</v>
       </c>
       <c r="U29" s="27">
-        <f>U28/U30</f>
+        <f t="shared" si="45"/>
         <v>0.53644742248170196</v>
       </c>
       <c r="V29" s="27">
-        <f>V28/V30</f>
+        <f t="shared" si="45"/>
         <v>0.71640189031493373</v>
       </c>
       <c r="W29" s="27">
-        <f>W28/W30</f>
+        <f t="shared" si="45"/>
         <v>0.97642945122509861</v>
       </c>
       <c r="X29" s="27"/>
       <c r="Y29" s="27"/>
       <c r="Z29" s="27"/>
-      <c r="AD29" s="1">
-        <f>+AD28/AD30</f>
+      <c r="AA29" s="27"/>
+      <c r="AB29" s="27"/>
+      <c r="AC29" s="27"/>
+      <c r="AD29" s="27"/>
+      <c r="AH29" s="1">
+        <f>+AH28/AH30</f>
         <v>-0.3800624444953335</v>
       </c>
-      <c r="AE29" s="1">
-        <f>+AE28/AE30</f>
+      <c r="AI29" s="1">
+        <f>+AI28/AI30</f>
         <v>-0.18948444787612517</v>
       </c>
-      <c r="AF29" s="1">
-        <f>+AF28/AF30</f>
+      <c r="AJ29" s="1">
+        <f>+AJ28/AJ30</f>
         <v>3.2176604757251086E-2</v>
       </c>
-      <c r="AG29" s="1">
-        <f>+AG28/AG30</f>
+      <c r="AK29" s="1">
+        <f>+AK28/AK30</f>
         <v>0.53444285431966365</v>
       </c>
-      <c r="AH29" s="1">
-        <f t="shared" ref="AH29:AO29" si="42">+AH28/AH30</f>
+      <c r="AL29" s="1">
+        <f t="shared" ref="AL29:AS29" si="46">+AL28/AL30</f>
         <v>5.4273939033820149</v>
       </c>
-      <c r="AI29" s="1">
-        <f t="shared" si="42"/>
+      <c r="AM29" s="1">
+        <f t="shared" si="46"/>
         <v>7.1673381602978399</v>
       </c>
-      <c r="AJ29" s="1">
-        <f t="shared" si="42"/>
+      <c r="AN29" s="1">
+        <f t="shared" si="46"/>
         <v>7.6235848058878517</v>
       </c>
-      <c r="AK29" s="1">
-        <f t="shared" si="42"/>
+      <c r="AO29" s="1">
+        <f t="shared" si="46"/>
         <v>7.1350310086835869</v>
       </c>
-      <c r="AL29" s="1">
-        <f t="shared" si="42"/>
+      <c r="AP29" s="1">
+        <f t="shared" si="46"/>
         <v>7.4906630166131389</v>
       </c>
-      <c r="AM29" s="1">
-        <f t="shared" si="42"/>
+      <c r="AQ29" s="1">
+        <f t="shared" si="46"/>
         <v>7.8723835448577342</v>
       </c>
-      <c r="AN29" s="1">
-        <f t="shared" si="42"/>
+      <c r="AR29" s="1">
+        <f t="shared" si="46"/>
         <v>8.2824375648292268</v>
       </c>
-      <c r="AO29" s="1">
-        <f t="shared" si="42"/>
+      <c r="AS29" s="1">
+        <f t="shared" si="46"/>
         <v>8.7046689054191351</v>
       </c>
     </row>
-    <row r="30" spans="2:122" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:126" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>1</v>
       </c>
@@ -5017,54 +5158,58 @@
       <c r="X30" s="25"/>
       <c r="Y30" s="25"/>
       <c r="Z30" s="25"/>
-      <c r="AD30" s="2">
+      <c r="AA30" s="25"/>
+      <c r="AB30" s="25"/>
+      <c r="AC30" s="25"/>
+      <c r="AD30" s="25"/>
+      <c r="AH30" s="2">
         <v>179.03899999999999</v>
       </c>
-      <c r="AE30" s="2">
+      <c r="AI30" s="2">
         <v>191.678</v>
       </c>
-      <c r="AF30" s="2">
+      <c r="AJ30" s="2">
         <f>AVERAGE(G30:J30)</f>
         <v>184.14000000000001</v>
       </c>
-      <c r="AG30" s="2">
+      <c r="AK30" s="2">
         <f>AVERAGE(K30:N30)</f>
         <v>188.48975000000002</v>
       </c>
-      <c r="AH30" s="2">
-        <f>+AG30</f>
+      <c r="AL30" s="2">
+        <f>+AK30</f>
         <v>188.48975000000002</v>
       </c>
-      <c r="AI30" s="2">
-        <f t="shared" ref="AI30:AO30" si="43">+AH30</f>
+      <c r="AM30" s="2">
+        <f t="shared" ref="AM30:AS30" si="47">+AL30</f>
         <v>188.48975000000002</v>
       </c>
-      <c r="AJ30" s="2">
-        <f t="shared" si="43"/>
+      <c r="AN30" s="2">
+        <f t="shared" si="47"/>
         <v>188.48975000000002</v>
       </c>
-      <c r="AK30" s="2">
-        <f t="shared" si="43"/>
+      <c r="AO30" s="2">
+        <f t="shared" si="47"/>
         <v>188.48975000000002</v>
       </c>
-      <c r="AL30" s="2">
-        <f t="shared" si="43"/>
+      <c r="AP30" s="2">
+        <f t="shared" si="47"/>
         <v>188.48975000000002</v>
       </c>
-      <c r="AM30" s="2">
-        <f t="shared" si="43"/>
+      <c r="AQ30" s="2">
+        <f t="shared" si="47"/>
         <v>188.48975000000002</v>
       </c>
-      <c r="AN30" s="2">
-        <f t="shared" si="43"/>
+      <c r="AR30" s="2">
+        <f t="shared" si="47"/>
         <v>188.48975000000002</v>
       </c>
-      <c r="AO30" s="2">
-        <f t="shared" si="43"/>
+      <c r="AS30" s="2">
+        <f t="shared" si="47"/>
         <v>188.48975000000002</v>
       </c>
     </row>
-    <row r="32" spans="2:122" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:126" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>170</v>
       </c>
@@ -5074,11 +5219,11 @@
       <c r="V32" s="16">
         <v>0.21</v>
       </c>
-      <c r="W32" s="49">
+      <c r="W32" s="16">
         <v>0.17</v>
       </c>
     </row>
-    <row r="33" spans="2:44" s="23" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:48" s="23" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B33" s="23" t="s">
         <v>75</v>
       </c>
@@ -5089,275 +5234,283 @@
       <c r="G33" s="24"/>
       <c r="H33" s="24"/>
       <c r="I33" s="28">
-        <f t="shared" ref="I33:N33" si="44">+I18/E18-1</f>
+        <f t="shared" ref="I33:N33" si="48">+I18/E18-1</f>
         <v>-0.14251074478282844</v>
       </c>
       <c r="J33" s="28">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>-5.0456564441062612E-3</v>
       </c>
       <c r="K33" s="28">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>6.8454370953439758E-2</v>
       </c>
       <c r="L33" s="28">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>6.3993318623142059E-2</v>
       </c>
       <c r="M33" s="28">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>0.23615833582027501</v>
       </c>
       <c r="N33" s="28">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>0.19510172502339995</v>
       </c>
       <c r="O33" s="28">
-        <f t="shared" ref="O33" si="45">+O18/K18-1</f>
+        <f t="shared" ref="O33" si="49">+O18/K18-1</f>
         <v>0.14842278764725614</v>
       </c>
       <c r="P33" s="28">
-        <f t="shared" ref="P33" si="46">+P18/L18-1</f>
+        <f t="shared" ref="P33" si="50">+P18/L18-1</f>
         <v>0.11516903397914557</v>
       </c>
       <c r="Q33" s="28">
-        <f t="shared" ref="Q33" si="47">+Q18/M18-1</f>
+        <f t="shared" ref="Q33" si="51">+Q18/M18-1</f>
         <v>0.15043020200101309</v>
       </c>
       <c r="R33" s="28">
-        <f t="shared" ref="R33" si="48">+R18/N18-1</f>
+        <f t="shared" ref="R33" si="52">+R18/N18-1</f>
         <v>0.2020534056620269</v>
       </c>
       <c r="S33" s="28">
-        <f t="shared" ref="S33" si="49">+S18/O18-1</f>
+        <f t="shared" ref="S33" si="53">+S18/O18-1</f>
         <v>8.7906910456645004E-2</v>
       </c>
       <c r="T33" s="28">
-        <f t="shared" ref="T33" si="50">+T18/P18-1</f>
+        <f t="shared" ref="T33" si="54">+T18/P18-1</f>
         <v>0.1961345596573012</v>
       </c>
       <c r="U33" s="28">
-        <f t="shared" ref="U33" si="51">+U18/Q18-1</f>
+        <f t="shared" ref="U33" si="55">+U18/Q18-1</f>
         <v>0.28297294461463851</v>
       </c>
       <c r="V33" s="28">
-        <f t="shared" ref="V33" si="52">+V18/R18-1</f>
+        <f t="shared" ref="V33" si="56">+V18/R18-1</f>
         <v>0.15556542584719857</v>
       </c>
       <c r="W33" s="28">
-        <f t="shared" ref="W32:Z33" si="53">+W18/S18-1</f>
+        <f t="shared" ref="W33:Z33" si="57">+W18/S18-1</f>
         <v>0.14742680829290222</v>
       </c>
       <c r="X33" s="28">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>0.10241689594103631</v>
       </c>
       <c r="Y33" s="28">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>0.1018940221726754</v>
       </c>
       <c r="Z33" s="28">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>0.1057348606295343</v>
       </c>
-      <c r="AE33" s="29">
-        <f>+AE18/AD18-1</f>
+      <c r="AA33" s="28"/>
+      <c r="AB33" s="28"/>
+      <c r="AC33" s="28"/>
+      <c r="AD33" s="28"/>
+      <c r="AI33" s="29">
+        <f>+AI18/AH18-1</f>
         <v>0.10560056609215063</v>
       </c>
-      <c r="AF33" s="29">
-        <f>+AF18/AE18-1</f>
+      <c r="AJ33" s="29">
+        <f>+AJ18/AI18-1</f>
         <v>-6.9633957835607552E-3</v>
       </c>
-      <c r="AG33" s="29">
-        <f>+AG18/AF18-1</f>
+      <c r="AK33" s="29">
+        <f>+AK18/AJ18-1</f>
         <v>0.13522647692985101</v>
       </c>
-      <c r="AH33" s="29">
-        <f t="shared" ref="AH33:AO33" si="54">+AH18/AG18-1</f>
+      <c r="AL33" s="29">
+        <f t="shared" ref="AL33:AS33" si="58">+AL18/AK18-1</f>
         <v>0.15419208386171546</v>
       </c>
-      <c r="AI33" s="29">
-        <f t="shared" si="54"/>
+      <c r="AM33" s="29">
+        <f t="shared" si="58"/>
         <v>0.17948530347898384</v>
       </c>
-      <c r="AJ33" s="29">
-        <f t="shared" si="54"/>
+      <c r="AN33" s="29">
+        <f t="shared" si="58"/>
         <v>0.11338332004520901</v>
       </c>
-      <c r="AK33" s="29">
-        <f t="shared" si="54"/>
+      <c r="AO33" s="29">
+        <f t="shared" si="58"/>
         <v>3.7515417746762258E-2</v>
       </c>
-      <c r="AL33" s="29">
-        <f t="shared" si="54"/>
+      <c r="AP33" s="29">
+        <f t="shared" si="58"/>
         <v>3.7195944629090816E-2</v>
       </c>
-      <c r="AM33" s="29">
-        <f t="shared" si="54"/>
+      <c r="AQ33" s="29">
+        <f t="shared" si="58"/>
         <v>3.8233396977213729E-2</v>
       </c>
-      <c r="AN33" s="29">
-        <f t="shared" si="54"/>
+      <c r="AR33" s="29">
+        <f t="shared" si="58"/>
         <v>3.9285846035489902E-2</v>
       </c>
-      <c r="AO33" s="29">
-        <f t="shared" si="54"/>
+      <c r="AS33" s="29">
+        <f t="shared" si="58"/>
         <v>3.884817236567728E-2</v>
       </c>
     </row>
-    <row r="34" spans="2:44" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:48" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>76</v>
       </c>
       <c r="E34" s="16">
-        <f t="shared" ref="E34:L34" si="55">+E20/E18</f>
+        <f t="shared" ref="E34:L34" si="59">+E20/E18</f>
         <v>0.6039941855465103</v>
       </c>
       <c r="F34" s="16">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v>0.72097807428905125</v>
       </c>
       <c r="G34" s="16">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v>0.75277588615420699</v>
       </c>
       <c r="H34" s="16">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v>0.74673356016528036</v>
       </c>
       <c r="I34" s="16">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v>0.74673069114143276</v>
       </c>
       <c r="J34" s="16">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v>0.73376523763258938</v>
       </c>
       <c r="K34" s="16">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v>0.77477885137503022</v>
       </c>
       <c r="L34" s="16">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v>0.7693397127752446</v>
       </c>
       <c r="M34" s="16">
-        <f t="shared" ref="M34:N34" si="56">+M20/M18</f>
+        <f t="shared" ref="M34:N34" si="60">+M20/M18</f>
         <v>0.76988348530901718</v>
       </c>
       <c r="N34" s="16">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v>0.7632016608811153</v>
       </c>
       <c r="O34" s="16">
-        <f t="shared" ref="O34:T34" si="57">+O20/O18</f>
+        <f t="shared" ref="O34:T34" si="61">+O20/O18</f>
         <v>0.77285614882254816</v>
       </c>
       <c r="P34" s="16">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v>0.88985594893116626</v>
       </c>
       <c r="Q34" s="16">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v>0.78542666113942572</v>
       </c>
       <c r="R34" s="16">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v>0.79033333900789127</v>
       </c>
       <c r="S34" s="16">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v>0.80707227006799775</v>
       </c>
       <c r="T34" s="16">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v>0.81677853008795998</v>
       </c>
       <c r="U34" s="16">
-        <f t="shared" ref="U34:V34" si="58">+U20/U18</f>
+        <f t="shared" ref="U34:V34" si="62">+U20/U18</f>
         <v>0.74733366136058021</v>
       </c>
       <c r="V34" s="16">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v>0.81767399377778138</v>
       </c>
       <c r="W34" s="16">
-        <f t="shared" ref="W34" si="59">+W20/W18</f>
+        <f t="shared" ref="W34" si="63">+W20/W18</f>
         <v>0.79643009210195825</v>
       </c>
       <c r="X34" s="16"/>
       <c r="Y34" s="16"/>
       <c r="Z34" s="16"/>
-      <c r="AD34" s="16">
-        <f>+AD20/AD18</f>
+      <c r="AA34" s="16"/>
+      <c r="AB34" s="16"/>
+      <c r="AC34" s="16"/>
+      <c r="AD34" s="16"/>
+      <c r="AH34" s="16">
+        <f>+AH20/AH18</f>
         <v>0.78624907459988524</v>
       </c>
-      <c r="AE34" s="16">
-        <f>+AE20/AE18</f>
+      <c r="AI34" s="16">
+        <f>+AI20/AI18</f>
         <v>0.71802630460809314</v>
       </c>
-      <c r="AF34" s="16">
-        <f>+AF20/AF18</f>
+      <c r="AJ34" s="16">
+        <f>+AJ20/AJ18</f>
         <v>0.74516437051106876</v>
       </c>
-      <c r="AG34" s="16">
-        <f>+AG20/AG18</f>
+      <c r="AK34" s="16">
+        <f>+AK20/AK18</f>
         <v>0.76924431136696081</v>
       </c>
-      <c r="AH34" s="16">
-        <f t="shared" ref="AH34:AO34" si="60">+AH20/AH18</f>
+      <c r="AL34" s="16">
+        <f t="shared" ref="AL34:AS34" si="64">+AL20/AL18</f>
         <v>0.78999999999999992</v>
       </c>
-      <c r="AI34" s="16">
-        <f t="shared" si="60"/>
+      <c r="AM34" s="16">
+        <f t="shared" si="64"/>
         <v>0.79000000000000015</v>
       </c>
-      <c r="AJ34" s="16">
-        <f t="shared" si="60"/>
+      <c r="AN34" s="16">
+        <f t="shared" si="64"/>
         <v>0.79</v>
       </c>
-      <c r="AK34" s="16">
-        <f t="shared" si="60"/>
+      <c r="AO34" s="16">
+        <f t="shared" si="64"/>
         <v>0.78999999999999992</v>
       </c>
-      <c r="AL34" s="16">
-        <f t="shared" si="60"/>
+      <c r="AP34" s="16">
+        <f t="shared" si="64"/>
         <v>0.78999999999999992</v>
       </c>
-      <c r="AM34" s="16">
-        <f t="shared" si="60"/>
+      <c r="AQ34" s="16">
+        <f t="shared" si="64"/>
         <v>0.79</v>
       </c>
-      <c r="AN34" s="16">
-        <f t="shared" si="60"/>
+      <c r="AR34" s="16">
+        <f t="shared" si="64"/>
         <v>0.78999999999999992</v>
       </c>
-      <c r="AO34" s="16">
-        <f t="shared" si="60"/>
+      <c r="AS34" s="16">
+        <f t="shared" si="64"/>
         <v>0.78999999999999992</v>
       </c>
-      <c r="AQ34" t="s">
+      <c r="AU34" t="s">
         <v>90</v>
       </c>
-      <c r="AR34" s="30">
+      <c r="AV34" s="30">
         <v>0.08</v>
       </c>
     </row>
-    <row r="35" spans="2:44" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:48" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>88</v>
       </c>
       <c r="H35" s="16"/>
       <c r="I35" s="16">
-        <f t="shared" ref="I35:K35" si="61">+I22/E22-1</f>
+        <f t="shared" ref="I35:K35" si="65">+I22/E22-1</f>
         <v>2.1638339370298132E-2</v>
       </c>
       <c r="J35" s="16">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v>0.11278591595400789</v>
       </c>
       <c r="K35" s="16">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v>0.11645957388221517</v>
       </c>
       <c r="L35" s="16">
@@ -5365,105 +5518,109 @@
         <v>6.8820217092652625E-2</v>
       </c>
       <c r="M35" s="16">
-        <f t="shared" ref="M35:N35" si="62">+M22/I22-1</f>
+        <f t="shared" ref="M35:N35" si="66">+M22/I22-1</f>
         <v>0.18263487751795915</v>
       </c>
       <c r="N35" s="16">
-        <f t="shared" si="62"/>
+        <f t="shared" si="66"/>
         <v>0.12950731512251634</v>
       </c>
       <c r="O35" s="16">
-        <f t="shared" ref="O35" si="63">+O22/K22-1</f>
+        <f t="shared" ref="O35" si="67">+O22/K22-1</f>
         <v>8.4287762243151931E-2</v>
       </c>
       <c r="P35" s="16">
-        <f t="shared" ref="P35" si="64">+P22/L22-1</f>
+        <f t="shared" ref="P35" si="68">+P22/L22-1</f>
         <v>4.7085122056544915E-2</v>
       </c>
       <c r="Q35" s="16">
-        <f t="shared" ref="Q35" si="65">+Q22/M22-1</f>
+        <f t="shared" ref="Q35" si="69">+Q22/M22-1</f>
         <v>3.2802007231938601E-2</v>
       </c>
       <c r="R35" s="16">
-        <f t="shared" ref="R35" si="66">+R22/N22-1</f>
+        <f t="shared" ref="R35" si="70">+R22/N22-1</f>
         <v>0.11917115313401605</v>
       </c>
       <c r="S35" s="16">
-        <f t="shared" ref="S35" si="67">+S22/O22-1</f>
+        <f t="shared" ref="S35" si="71">+S22/O22-1</f>
         <v>7.0527857153011908E-2</v>
       </c>
       <c r="T35" s="16">
-        <f t="shared" ref="T35" si="68">+T22/P22-1</f>
+        <f t="shared" ref="T35" si="72">+T22/P22-1</f>
         <v>0.27621626080163786</v>
       </c>
       <c r="U35" s="16">
-        <f t="shared" ref="U35" si="69">+U22/Q22-1</f>
+        <f t="shared" ref="U35" si="73">+U22/Q22-1</f>
         <v>-0.17428369833160651</v>
       </c>
       <c r="V35" s="16">
-        <f t="shared" ref="V35" si="70">+V22/R22-1</f>
+        <f t="shared" ref="V35" si="74">+V22/R22-1</f>
         <v>-3.0604601780208185E-2</v>
       </c>
       <c r="W35" s="16">
-        <f t="shared" ref="W35" si="71">+W22/S22-1</f>
+        <f t="shared" ref="W35" si="75">+W22/S22-1</f>
         <v>-8.7602808247678188E-2</v>
       </c>
       <c r="X35" s="16"/>
       <c r="Y35" s="16"/>
       <c r="Z35" s="16"/>
       <c r="AA35" s="16"/>
-      <c r="AE35" s="16">
-        <f>+AE22/AD22-1</f>
+      <c r="AB35" s="16"/>
+      <c r="AC35" s="16"/>
+      <c r="AD35" s="16"/>
+      <c r="AE35" s="16"/>
+      <c r="AI35" s="16">
+        <f>+AI22/AH22-1</f>
         <v>8.3335291456902771E-2</v>
       </c>
-      <c r="AF35" s="16">
-        <f>+AF22/AE22-1</f>
+      <c r="AJ35" s="16">
+        <f>+AJ22/AI22-1</f>
         <v>2.9425121565363366E-2</v>
       </c>
-      <c r="AG35" s="16">
-        <f>+AG22/AF22-1</f>
+      <c r="AK35" s="16">
+        <f>+AK22/AJ22-1</f>
         <v>0.1246209053497942</v>
       </c>
-      <c r="AH35" s="16">
-        <f t="shared" ref="AH35:AO35" si="72">+AH22/AG22-1</f>
+      <c r="AL35" s="16">
+        <f t="shared" ref="AL35:AS35" si="76">+AL22/AK22-1</f>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AI35" s="16">
-        <f t="shared" si="72"/>
+      <c r="AM35" s="16">
+        <f t="shared" si="76"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AJ35" s="16">
-        <f t="shared" si="72"/>
+      <c r="AN35" s="16">
+        <f t="shared" si="76"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AK35" s="16">
-        <f t="shared" si="72"/>
+      <c r="AO35" s="16">
+        <f t="shared" si="76"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AL35" s="16">
-        <f t="shared" si="72"/>
+      <c r="AP35" s="16">
+        <f t="shared" si="76"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AM35" s="16">
-        <f t="shared" si="72"/>
+      <c r="AQ35" s="16">
+        <f t="shared" si="76"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AN35" s="16">
-        <f t="shared" si="72"/>
+      <c r="AR35" s="16">
+        <f t="shared" si="76"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AO35" s="16">
-        <f t="shared" si="72"/>
+      <c r="AS35" s="16">
+        <f t="shared" si="76"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AQ35" t="s">
+      <c r="AU35" t="s">
         <v>91</v>
       </c>
-      <c r="AR35" s="30">
+      <c r="AV35" s="30">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="36" spans="2:44" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:48" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>89</v>
       </c>
@@ -5480,102 +5637,102 @@
         <v>-2.6871401151631558E-2</v>
       </c>
       <c r="O36" s="16">
-        <f t="shared" ref="O36:T36" si="73">+O8/K8-1</f>
+        <f t="shared" ref="O36:T36" si="77">+O8/K8-1</f>
         <v>3.3836065573770613E-2</v>
       </c>
       <c r="P36" s="16">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>2.4167754003902919E-2</v>
       </c>
       <c r="Q36" s="16">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>2.2062134173795656E-2</v>
       </c>
       <c r="R36" s="16">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>0.15450361604207763</v>
       </c>
       <c r="S36" s="16">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>1.7590595796862507E-2</v>
       </c>
       <c r="T36" s="16">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>3.5176332641833064E-3</v>
       </c>
       <c r="U36" s="16">
-        <f t="shared" ref="U36" si="74">+U8/Q8-1</f>
+        <f t="shared" ref="U36" si="78">+U8/Q8-1</f>
         <v>0.12020138451856499</v>
       </c>
       <c r="V36" s="16">
-        <f t="shared" ref="V36" si="75">+V8/R8-1</f>
+        <f t="shared" ref="V36" si="79">+V8/R8-1</f>
         <v>8.7699316628701673E-2</v>
       </c>
       <c r="W36" s="16">
-        <f t="shared" ref="W36" si="76">+W8/S8-1</f>
+        <f t="shared" ref="W36" si="80">+W8/S8-1</f>
         <v>-2.347808019945985E-2</v>
       </c>
-      <c r="AE36" s="30">
-        <f>+AE8/AD8-1</f>
+      <c r="AI36" s="30">
+        <f>+AI8/AH8-1</f>
         <v>1.8372221201556904E-4</v>
       </c>
-      <c r="AF36" s="30">
-        <f>+AF8/AE8-1</f>
+      <c r="AJ36" s="30">
+        <f>+AJ8/AI8-1</f>
         <v>0.14484753857457777</v>
       </c>
-      <c r="AG36" s="30">
-        <f>+AG8/AF8-1</f>
+      <c r="AK36" s="30">
+        <f>+AK8/AJ8-1</f>
         <v>6.5015122221241617E-2</v>
       </c>
-      <c r="AH36" s="30">
-        <f t="shared" ref="AH36:AO36" si="77">+AH8/AG8-1</f>
+      <c r="AL36" s="30">
+        <f t="shared" ref="AL36:AS36" si="81">+AL8/AK8-1</f>
         <v>5.6205707949669836E-2</v>
       </c>
-      <c r="AI36" s="30">
-        <f t="shared" si="77"/>
+      <c r="AM36" s="30">
+        <f t="shared" si="81"/>
         <v>5.4846494856536365E-2</v>
       </c>
-      <c r="AJ36" s="30">
-        <f t="shared" si="77"/>
+      <c r="AN36" s="30">
+        <f t="shared" si="81"/>
         <v>3.0871789879059142E-2</v>
       </c>
-      <c r="AK36" s="30">
-        <f t="shared" si="77"/>
+      <c r="AO36" s="30">
+        <f t="shared" si="81"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AL36" s="30">
-        <f t="shared" si="77"/>
+      <c r="AP36" s="30">
+        <f t="shared" si="81"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AM36" s="30">
-        <f t="shared" si="77"/>
+      <c r="AQ36" s="30">
+        <f t="shared" si="81"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AN36" s="30">
-        <f t="shared" si="77"/>
+      <c r="AR36" s="30">
+        <f t="shared" si="81"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AO36" s="30">
-        <f t="shared" si="77"/>
+      <c r="AS36" s="30">
+        <f t="shared" si="81"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AQ36" t="s">
+      <c r="AU36" t="s">
         <v>95</v>
       </c>
-      <c r="AR36" s="30">
+      <c r="AV36" s="30">
         <v>0.02</v>
       </c>
     </row>
-    <row r="37" spans="2:44" x14ac:dyDescent="0.25">
-      <c r="AQ37" t="s">
+    <row r="37" spans="2:48" x14ac:dyDescent="0.25">
+      <c r="AU37" t="s">
         <v>92</v>
       </c>
-      <c r="AR37" s="2">
-        <f>NPV(AR34,AH28:DR28)+Main!L5-Main!L6</f>
+      <c r="AV37" s="2">
+        <f>NPV(AV34,AL28:DV28)+Main!L5-Main!L6</f>
         <v>18853.455038609995</v>
       </c>
     </row>
-    <row r="38" spans="2:44" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:48" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>94</v>
       </c>
@@ -5603,51 +5760,55 @@
       <c r="X38" s="25"/>
       <c r="Y38" s="25"/>
       <c r="Z38" s="25"/>
-      <c r="AG38" s="2">
+      <c r="AA38" s="25"/>
+      <c r="AB38" s="25"/>
+      <c r="AC38" s="25"/>
+      <c r="AD38" s="25"/>
+      <c r="AK38" s="2">
         <f>+N38</f>
         <v>0</v>
       </c>
-      <c r="AH38" s="2">
-        <f>+AG38+AH28</f>
+      <c r="AL38" s="2">
+        <f>+AK38+AL28</f>
         <v>1023.0081200000002</v>
       </c>
-      <c r="AI38" s="2">
-        <f t="shared" ref="AI38:AO38" si="78">+AH38+AI28</f>
+      <c r="AM38" s="2">
+        <f t="shared" ref="AM38:AS38" si="82">+AL38+AM28</f>
         <v>2373.9778980000001</v>
       </c>
-      <c r="AJ38" s="2">
-        <f t="shared" si="78"/>
+      <c r="AN38" s="2">
+        <f t="shared" si="82"/>
         <v>3810.9454921655997</v>
       </c>
-      <c r="AK38" s="2">
-        <f t="shared" si="78"/>
+      <c r="AO38" s="2">
+        <f t="shared" si="82"/>
         <v>5155.8257032346173</v>
       </c>
-      <c r="AL38" s="2">
-        <f t="shared" si="78"/>
+      <c r="AP38" s="2">
+        <f t="shared" si="82"/>
         <v>6567.7389025702741</v>
       </c>
-      <c r="AM38" s="2">
-        <f t="shared" si="78"/>
+      <c r="AQ38" s="2">
+        <f t="shared" si="82"/>
         <v>8051.6025088446222</v>
       </c>
-      <c r="AN38" s="2">
-        <f t="shared" si="78"/>
+      <c r="AR38" s="2">
+        <f t="shared" si="82"/>
         <v>9612.7570948298926</v>
       </c>
-      <c r="AO38" s="2">
-        <f t="shared" si="78"/>
+      <c r="AS38" s="2">
+        <f t="shared" si="82"/>
         <v>11253.49796064512</v>
       </c>
-      <c r="AQ38" t="s">
+      <c r="AU38" t="s">
         <v>93</v>
       </c>
-      <c r="AR38" s="1">
-        <f>+AR37/Main!L3</f>
+      <c r="AV38" s="1">
+        <f>+AV37/Main!L3</f>
         <v>96.191097135765276</v>
       </c>
     </row>
-    <row r="39" spans="2:44" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:48" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B39" s="2" t="s">
         <v>3</v>
       </c>
@@ -5684,12 +5845,16 @@
       <c r="X39" s="25"/>
       <c r="Y39" s="25"/>
       <c r="Z39" s="25"/>
-      <c r="AR39" s="30">
-        <f>+AR38/Main!L2-1</f>
+      <c r="AA39" s="25"/>
+      <c r="AB39" s="25"/>
+      <c r="AC39" s="25"/>
+      <c r="AD39" s="25"/>
+      <c r="AV39" s="30">
+        <f>+AV38/Main!L2-1</f>
         <v>0.63284836421261725</v>
       </c>
     </row>
-    <row r="40" spans="2:44" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:48" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B40" s="2" t="s">
         <v>130</v>
       </c>
@@ -5723,8 +5888,12 @@
       <c r="X40" s="25"/>
       <c r="Y40" s="25"/>
       <c r="Z40" s="25"/>
-    </row>
-    <row r="41" spans="2:44" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA40" s="25"/>
+      <c r="AB40" s="25"/>
+      <c r="AC40" s="25"/>
+      <c r="AD40" s="25"/>
+    </row>
+    <row r="41" spans="2:48" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B41" s="2" t="s">
         <v>131</v>
       </c>
@@ -5758,8 +5927,12 @@
       <c r="X41" s="25"/>
       <c r="Y41" s="25"/>
       <c r="Z41" s="25"/>
-    </row>
-    <row r="42" spans="2:44" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA41" s="25"/>
+      <c r="AB41" s="25"/>
+      <c r="AC41" s="25"/>
+      <c r="AD41" s="25"/>
+    </row>
+    <row r="42" spans="2:48" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B42" s="2" t="s">
         <v>132</v>
       </c>
@@ -5793,8 +5966,12 @@
       <c r="X42" s="25"/>
       <c r="Y42" s="25"/>
       <c r="Z42" s="25"/>
-    </row>
-    <row r="43" spans="2:44" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA42" s="25"/>
+      <c r="AB42" s="25"/>
+      <c r="AC42" s="25"/>
+      <c r="AD42" s="25"/>
+    </row>
+    <row r="43" spans="2:48" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B43" s="2" t="s">
         <v>133</v>
       </c>
@@ -5828,8 +6005,12 @@
       <c r="X43" s="25"/>
       <c r="Y43" s="25"/>
       <c r="Z43" s="25"/>
-    </row>
-    <row r="44" spans="2:44" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA43" s="25"/>
+      <c r="AB43" s="25"/>
+      <c r="AC43" s="25"/>
+      <c r="AD43" s="25"/>
+    </row>
+    <row r="44" spans="2:48" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B44" s="2" t="s">
         <v>134</v>
       </c>
@@ -5866,8 +6047,12 @@
       <c r="X44" s="25"/>
       <c r="Y44" s="25"/>
       <c r="Z44" s="25"/>
-    </row>
-    <row r="45" spans="2:44" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA44" s="25"/>
+      <c r="AB44" s="25"/>
+      <c r="AC44" s="25"/>
+      <c r="AD44" s="25"/>
+    </row>
+    <row r="45" spans="2:48" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B45" s="2" t="s">
         <v>135</v>
       </c>
@@ -5901,8 +6086,12 @@
       <c r="X45" s="25"/>
       <c r="Y45" s="25"/>
       <c r="Z45" s="25"/>
-    </row>
-    <row r="46" spans="2:44" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA45" s="25"/>
+      <c r="AB45" s="25"/>
+      <c r="AC45" s="25"/>
+      <c r="AD45" s="25"/>
+    </row>
+    <row r="46" spans="2:48" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B46" s="2" t="s">
         <v>136</v>
       </c>
@@ -5936,8 +6125,12 @@
       <c r="X46" s="25"/>
       <c r="Y46" s="25"/>
       <c r="Z46" s="25"/>
-    </row>
-    <row r="47" spans="2:44" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA46" s="25"/>
+      <c r="AB46" s="25"/>
+      <c r="AC46" s="25"/>
+      <c r="AD46" s="25"/>
+    </row>
+    <row r="47" spans="2:48" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B47" s="2" t="s">
         <v>137</v>
       </c>
@@ -5956,50 +6149,54 @@
         <v>6264.0400000000009</v>
       </c>
       <c r="N47" s="25">
-        <f t="shared" ref="N47:W47" si="79">SUM(N39:N46)</f>
+        <f t="shared" ref="N47:W47" si="83">SUM(N39:N46)</f>
         <v>0</v>
       </c>
       <c r="O47" s="25">
-        <f t="shared" si="79"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="P47" s="25">
-        <f t="shared" si="79"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="Q47" s="25">
-        <f t="shared" si="79"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="R47" s="25">
-        <f t="shared" si="79"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="S47" s="25">
-        <f t="shared" si="79"/>
+        <f t="shared" si="83"/>
         <v>6872.6729999999989</v>
       </c>
       <c r="T47" s="25">
-        <f t="shared" si="79"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="U47" s="25">
-        <f t="shared" si="79"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="V47" s="25">
-        <f t="shared" si="79"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="W47" s="25">
-        <f t="shared" si="79"/>
+        <f t="shared" si="83"/>
         <v>7147.0069999999996</v>
       </c>
       <c r="X47" s="25"/>
       <c r="Y47" s="25"/>
       <c r="Z47" s="25"/>
-    </row>
-    <row r="49" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA47" s="25"/>
+      <c r="AB47" s="25"/>
+      <c r="AC47" s="25"/>
+      <c r="AD47" s="25"/>
+    </row>
+    <row r="49" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B49" s="2" t="s">
         <v>138</v>
       </c>
@@ -6033,8 +6230,12 @@
       <c r="X49" s="25"/>
       <c r="Y49" s="25"/>
       <c r="Z49" s="25"/>
-    </row>
-    <row r="50" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA49" s="25"/>
+      <c r="AB49" s="25"/>
+      <c r="AC49" s="25"/>
+      <c r="AD49" s="25"/>
+    </row>
+    <row r="50" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B50" s="2" t="s">
         <v>139</v>
       </c>
@@ -6068,8 +6269,12 @@
       <c r="X50" s="25"/>
       <c r="Y50" s="25"/>
       <c r="Z50" s="25"/>
-    </row>
-    <row r="51" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA50" s="25"/>
+      <c r="AB50" s="25"/>
+      <c r="AC50" s="25"/>
+      <c r="AD50" s="25"/>
+    </row>
+    <row r="51" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B51" s="2" t="s">
         <v>4</v>
       </c>
@@ -6104,8 +6309,12 @@
       <c r="X51" s="25"/>
       <c r="Y51" s="25"/>
       <c r="Z51" s="25"/>
-    </row>
-    <row r="52" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA51" s="25"/>
+      <c r="AB51" s="25"/>
+      <c r="AC51" s="25"/>
+      <c r="AD51" s="25"/>
+    </row>
+    <row r="52" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B52" s="2" t="s">
         <v>140</v>
       </c>
@@ -6139,8 +6348,12 @@
       <c r="X52" s="25"/>
       <c r="Y52" s="25"/>
       <c r="Z52" s="25"/>
-    </row>
-    <row r="53" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA52" s="25"/>
+      <c r="AB52" s="25"/>
+      <c r="AC52" s="25"/>
+      <c r="AD52" s="25"/>
+    </row>
+    <row r="53" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B53" s="2" t="s">
         <v>129</v>
       </c>
@@ -6174,8 +6387,12 @@
       <c r="X53" s="25"/>
       <c r="Y53" s="25"/>
       <c r="Z53" s="25"/>
-    </row>
-    <row r="54" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA53" s="25"/>
+      <c r="AB53" s="25"/>
+      <c r="AC53" s="25"/>
+      <c r="AD53" s="25"/>
+    </row>
+    <row r="54" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B54" s="2" t="s">
         <v>128</v>
       </c>
@@ -6194,50 +6411,54 @@
         <v>6264.04</v>
       </c>
       <c r="N54" s="25">
-        <f t="shared" ref="N54:W54" si="80">SUM(N49:N53)</f>
+        <f t="shared" ref="N54:W54" si="84">SUM(N49:N53)</f>
         <v>0</v>
       </c>
       <c r="O54" s="25">
-        <f t="shared" si="80"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="P54" s="25">
-        <f t="shared" si="80"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="Q54" s="25">
-        <f t="shared" si="80"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="R54" s="25">
-        <f t="shared" si="80"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="S54" s="25">
-        <f t="shared" si="80"/>
+        <f t="shared" si="84"/>
         <v>6872.6729999999998</v>
       </c>
       <c r="T54" s="25">
-        <f t="shared" si="80"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="U54" s="25">
-        <f t="shared" si="80"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="V54" s="25">
-        <f t="shared" si="80"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="W54" s="25">
-        <f t="shared" si="80"/>
+        <f t="shared" si="84"/>
         <v>7147.0069999999996</v>
       </c>
       <c r="X54" s="25"/>
       <c r="Y54" s="25"/>
       <c r="Z54" s="25"/>
-    </row>
-    <row r="56" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA54" s="25"/>
+      <c r="AB54" s="25"/>
+      <c r="AC54" s="25"/>
+      <c r="AD54" s="25"/>
+    </row>
+    <row r="56" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B56" s="2" t="s">
         <v>156</v>
       </c>
@@ -6268,8 +6489,12 @@
       <c r="X56" s="25"/>
       <c r="Y56" s="25"/>
       <c r="Z56" s="25"/>
-    </row>
-    <row r="57" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA56" s="25"/>
+      <c r="AB56" s="25"/>
+      <c r="AC56" s="25"/>
+      <c r="AD56" s="25"/>
+    </row>
+    <row r="57" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B57" s="2" t="s">
         <v>157</v>
       </c>
@@ -6299,8 +6524,12 @@
       <c r="X57" s="25"/>
       <c r="Y57" s="25"/>
       <c r="Z57" s="25"/>
-    </row>
-    <row r="58" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA57" s="25"/>
+      <c r="AB57" s="25"/>
+      <c r="AC57" s="25"/>
+      <c r="AD57" s="25"/>
+    </row>
+    <row r="58" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B58" s="2" t="s">
         <v>161</v>
       </c>
@@ -6330,8 +6559,12 @@
       <c r="X58" s="25"/>
       <c r="Y58" s="25"/>
       <c r="Z58" s="25"/>
-    </row>
-    <row r="59" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA58" s="25"/>
+      <c r="AB58" s="25"/>
+      <c r="AC58" s="25"/>
+      <c r="AD58" s="25"/>
+    </row>
+    <row r="59" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B59" s="2" t="s">
         <v>162</v>
       </c>
@@ -6361,8 +6594,12 @@
       <c r="X59" s="25"/>
       <c r="Y59" s="25"/>
       <c r="Z59" s="25"/>
-    </row>
-    <row r="60" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA59" s="25"/>
+      <c r="AB59" s="25"/>
+      <c r="AC59" s="25"/>
+      <c r="AD59" s="25"/>
+    </row>
+    <row r="60" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B60" s="2" t="s">
         <v>163</v>
       </c>
@@ -6392,8 +6629,12 @@
       <c r="X60" s="25"/>
       <c r="Y60" s="25"/>
       <c r="Z60" s="25"/>
-    </row>
-    <row r="61" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA60" s="25"/>
+      <c r="AB60" s="25"/>
+      <c r="AC60" s="25"/>
+      <c r="AD60" s="25"/>
+    </row>
+    <row r="61" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B61" s="2" t="s">
         <v>164</v>
       </c>
@@ -6423,8 +6664,12 @@
       <c r="X61" s="25"/>
       <c r="Y61" s="25"/>
       <c r="Z61" s="25"/>
-    </row>
-    <row r="62" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA61" s="25"/>
+      <c r="AB61" s="25"/>
+      <c r="AC61" s="25"/>
+      <c r="AD61" s="25"/>
+    </row>
+    <row r="62" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B62" s="2" t="s">
         <v>165</v>
       </c>
@@ -6454,8 +6699,12 @@
       <c r="X62" s="25"/>
       <c r="Y62" s="25"/>
       <c r="Z62" s="25"/>
-    </row>
-    <row r="63" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA62" s="25"/>
+      <c r="AB62" s="25"/>
+      <c r="AC62" s="25"/>
+      <c r="AD62" s="25"/>
+    </row>
+    <row r="63" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B63" s="2" t="s">
         <v>135</v>
       </c>
@@ -6485,8 +6734,12 @@
       <c r="X63" s="25"/>
       <c r="Y63" s="25"/>
       <c r="Z63" s="25"/>
-    </row>
-    <row r="64" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA63" s="25"/>
+      <c r="AB63" s="25"/>
+      <c r="AC63" s="25"/>
+      <c r="AD63" s="25"/>
+    </row>
+    <row r="64" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B64" s="2" t="s">
         <v>166</v>
       </c>
@@ -6516,8 +6769,12 @@
       <c r="X64" s="25"/>
       <c r="Y64" s="25"/>
       <c r="Z64" s="25"/>
-    </row>
-    <row r="65" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA64" s="25"/>
+      <c r="AB64" s="25"/>
+      <c r="AC64" s="25"/>
+      <c r="AD64" s="25"/>
+    </row>
+    <row r="65" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B65" s="2" t="s">
         <v>136</v>
       </c>
@@ -6547,8 +6804,12 @@
       <c r="X65" s="25"/>
       <c r="Y65" s="25"/>
       <c r="Z65" s="25"/>
-    </row>
-    <row r="66" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA65" s="25"/>
+      <c r="AB65" s="25"/>
+      <c r="AC65" s="25"/>
+      <c r="AD65" s="25"/>
+    </row>
+    <row r="66" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B66" s="2" t="s">
         <v>167</v>
       </c>
@@ -6579,8 +6840,12 @@
       <c r="X66" s="25"/>
       <c r="Y66" s="25"/>
       <c r="Z66" s="25"/>
-    </row>
-    <row r="67" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA66" s="25"/>
+      <c r="AB66" s="25"/>
+      <c r="AC66" s="25"/>
+      <c r="AD66" s="25"/>
+    </row>
+    <row r="67" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B67" s="2" t="s">
         <v>150</v>
       </c>
@@ -6615,8 +6880,12 @@
       <c r="X67" s="25"/>
       <c r="Y67" s="25"/>
       <c r="Z67" s="25"/>
-    </row>
-    <row r="68" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA67" s="25"/>
+      <c r="AB67" s="25"/>
+      <c r="AC67" s="25"/>
+      <c r="AD67" s="25"/>
+    </row>
+    <row r="68" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C68" s="25"/>
       <c r="D68" s="25"/>
       <c r="E68" s="25"/>
@@ -6641,8 +6910,12 @@
       <c r="X68" s="25"/>
       <c r="Y68" s="25"/>
       <c r="Z68" s="25"/>
-    </row>
-    <row r="69" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA68" s="25"/>
+      <c r="AB68" s="25"/>
+      <c r="AC68" s="25"/>
+      <c r="AD68" s="25"/>
+    </row>
+    <row r="69" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B69" s="2" t="s">
         <v>133</v>
       </c>
@@ -6672,8 +6945,12 @@
       <c r="X69" s="25"/>
       <c r="Y69" s="25"/>
       <c r="Z69" s="25"/>
-    </row>
-    <row r="70" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA69" s="25"/>
+      <c r="AB69" s="25"/>
+      <c r="AC69" s="25"/>
+      <c r="AD69" s="25"/>
+    </row>
+    <row r="70" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B70" s="2" t="s">
         <v>169</v>
       </c>
@@ -6704,8 +6981,12 @@
       <c r="X70" s="25"/>
       <c r="Y70" s="25"/>
       <c r="Z70" s="25"/>
-    </row>
-    <row r="71" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA70" s="25"/>
+      <c r="AB70" s="25"/>
+      <c r="AC70" s="25"/>
+      <c r="AD70" s="25"/>
+    </row>
+    <row r="71" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B71" s="2" t="s">
         <v>168</v>
       </c>
@@ -6736,8 +7017,12 @@
       <c r="X71" s="25"/>
       <c r="Y71" s="25"/>
       <c r="Z71" s="25"/>
-    </row>
-    <row r="72" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA71" s="25"/>
+      <c r="AB71" s="25"/>
+      <c r="AC71" s="25"/>
+      <c r="AD71" s="25"/>
+    </row>
+    <row r="72" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C72" s="25"/>
       <c r="D72" s="25"/>
       <c r="E72" s="25"/>
@@ -6762,8 +7047,12 @@
       <c r="X72" s="25"/>
       <c r="Y72" s="25"/>
       <c r="Z72" s="25"/>
-    </row>
-    <row r="73" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA72" s="25"/>
+      <c r="AB72" s="25"/>
+      <c r="AC72" s="25"/>
+      <c r="AD72" s="25"/>
+    </row>
+    <row r="73" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B73" s="2" t="s">
         <v>160</v>
       </c>
@@ -6793,8 +7082,12 @@
       <c r="X73" s="25"/>
       <c r="Y73" s="25"/>
       <c r="Z73" s="25"/>
-    </row>
-    <row r="74" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA73" s="25"/>
+      <c r="AB73" s="25"/>
+      <c r="AC73" s="25"/>
+      <c r="AD73" s="25"/>
+    </row>
+    <row r="74" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B74" s="2" t="s">
         <v>159</v>
       </c>
@@ -6824,8 +7117,12 @@
       <c r="X74" s="25"/>
       <c r="Y74" s="25"/>
       <c r="Z74" s="25"/>
-    </row>
-    <row r="75" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA74" s="25"/>
+      <c r="AB74" s="25"/>
+      <c r="AC74" s="25"/>
+      <c r="AD74" s="25"/>
+    </row>
+    <row r="75" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B75" s="2" t="s">
         <v>158</v>
       </c>
@@ -6856,6 +7153,10 @@
       <c r="X75" s="25"/>
       <c r="Y75" s="25"/>
       <c r="Z75" s="25"/>
+      <c r="AA75" s="25"/>
+      <c r="AB75" s="25"/>
+      <c r="AC75" s="25"/>
+      <c r="AD75" s="25"/>
     </row>
   </sheetData>
   <hyperlinks>
